--- a/TS Jatai Working/TTD Krama PaaraayaNam.xlsx
+++ b/TS Jatai Working/TTD Krama PaaraayaNam.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0097E86C-A1A2-4639-9BBE-45C99B6AB161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D53DD99-6633-42D2-87E0-A331E8C53A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1301,10 +1301,10 @@
   </cellStyleXfs>
   <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
@@ -1327,14 +1327,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1402,7 +1401,7 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1456,7 +1455,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1475,13 +1474,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1508,7 +1507,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1517,16 +1516,16 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1535,7 +1534,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1544,7 +1543,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1565,12 +1564,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1590,9 +1590,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1630,9 +1630,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1665,26 +1665,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1717,26 +1700,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1914,116 +1880,115 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1"/>
-    <col min="2" max="2" width="15.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="86" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="101" customWidth="1"/>
-    <col min="7" max="7" width="20.5703125" style="17" customWidth="1"/>
-    <col min="8" max="8" width="138.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="15"/>
+    <col min="2" max="2" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="85" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="100" customWidth="1"/>
+    <col min="7" max="7" width="20.5703125" style="16" customWidth="1"/>
+    <col min="8" max="8" width="138.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="70" t="s">
+      <c r="D1" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="87" t="s">
+      <c r="E1" s="23"/>
+      <c r="F1" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="41" t="s">
+      <c r="G1" s="24"/>
+      <c r="H1" s="40" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="14"/>
       <c r="J1" s="14"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="21"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="71" t="s">
+      <c r="A2" s="20"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="70" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="13"/>
-      <c r="F2" s="88" t="s">
+      <c r="F2" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="42"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="41"/>
       <c r="I2" s="14"/>
       <c r="J2" s="14"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="21"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="71" t="s">
+      <c r="A3" s="20"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="70" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="89" t="s">
+      <c r="F3" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
       <c r="I3" s="14"/>
       <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="72" t="s">
+      <c r="D4" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="90" t="s">
+      <c r="E4" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="43"/>
+      <c r="H4" s="42"/>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="29">
+      <c r="A5" s="28">
         <v>1</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="31">
         <v>44446</v>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="36">
         <v>1</v>
       </c>
-      <c r="D5" s="73" t="s">
+      <c r="D5" s="72" t="s">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="91" t="s">
+      <c r="F5" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="51" t="s">
+      <c r="G5" s="50" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -2035,13 +2000,13 @@
       <c r="L5" s="14"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="74"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="73"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="52"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="51"/>
       <c r="H6" s="7"/>
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
@@ -2049,25 +2014,25 @@
       <c r="L6" s="14"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="29">
+      <c r="A7" s="28">
         <v>2</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="31">
         <v>44447</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="36">
         <v>1</v>
       </c>
-      <c r="D7" s="75" t="s">
+      <c r="D7" s="74" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="93" t="s">
+      <c r="F7" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="51" t="s">
+      <c r="G7" s="50" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="10" t="s">
@@ -2079,13 +2044,13 @@
       <c r="L7" s="14"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="76"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="75"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="52"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="51"/>
       <c r="H8" s="12"/>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
@@ -2093,28 +2058,28 @@
       <c r="L8" s="14"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>3</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="31">
         <v>44448</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="36">
         <v>2</v>
       </c>
-      <c r="D9" s="75" t="s">
+      <c r="D9" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="93" t="s">
+      <c r="F9" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="53" t="s">
+      <c r="H9" s="52" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="14"/>
@@ -2123,26 +2088,26 @@
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="31"/>
-      <c r="B10" s="34">
+      <c r="A10" s="30"/>
+      <c r="B10" s="33">
         <v>44448</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="35">
         <v>1</v>
       </c>
-      <c r="D10" s="64" t="s">
+      <c r="D10" s="63" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="94" t="s">
+      <c r="F10" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="54" t="s">
+      <c r="G10" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="53" t="s">
         <v>21</v>
       </c>
       <c r="I10" s="14"/>
@@ -2151,39 +2116,39 @@
       <c r="L10" s="14"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="76"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="75"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="55"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="54"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="29">
+      <c r="A12" s="28">
         <v>4</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="31">
         <v>44449</v>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="36">
         <v>2</v>
       </c>
-      <c r="D12" s="75" t="s">
+      <c r="D12" s="74" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="93" t="s">
+      <c r="F12" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="56" t="s">
+      <c r="G12" s="55" t="s">
         <v>13</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -2195,13 +2160,13 @@
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="76"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="75"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="92"/>
-      <c r="G13" s="30"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="29"/>
       <c r="H13" s="11"/>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
@@ -2209,25 +2174,25 @@
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="29">
+      <c r="A14" s="28">
         <v>5</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="31">
         <v>44450</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="36">
         <v>1</v>
       </c>
-      <c r="D14" s="75" t="s">
+      <c r="D14" s="74" t="s">
         <v>29</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="93" t="s">
+      <c r="F14" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="56" t="s">
+      <c r="G14" s="55" t="s">
         <v>13</v>
       </c>
       <c r="H14" s="10" t="s">
@@ -2239,13 +2204,13 @@
       <c r="L14" s="14"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="76"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="75"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="44"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="43"/>
       <c r="H15" s="12"/>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
@@ -2253,28 +2218,28 @@
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="29">
+      <c r="A16" s="28">
         <v>6</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="31">
         <v>44451</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="36">
         <v>2</v>
       </c>
-      <c r="D16" s="75" t="s">
+      <c r="D16" s="74" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="93" t="s">
+      <c r="F16" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="53" t="s">
+      <c r="H16" s="52" t="s">
         <v>33</v>
       </c>
       <c r="I16" s="14"/>
@@ -2283,26 +2248,26 @@
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="B17" s="34">
+      <c r="A17" s="30"/>
+      <c r="B17" s="33">
         <v>44451</v>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="35">
         <v>1</v>
       </c>
-      <c r="D17" s="64" t="s">
+      <c r="D17" s="63" t="s">
         <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="94" t="s">
+      <c r="F17" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="54" t="s">
+      <c r="G17" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="53" t="s">
         <v>33</v>
       </c>
       <c r="I17" s="14"/>
@@ -2311,39 +2276,39 @@
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="64"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="63"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="55"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="54"/>
       <c r="I18" s="14"/>
       <c r="J18" s="14"/>
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="29">
+      <c r="A19" s="28">
         <v>7</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="31">
         <v>44452</v>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="57">
         <v>2</v>
       </c>
-      <c r="D19" s="77" t="s">
+      <c r="D19" s="76" t="s">
         <v>38</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="93" t="s">
+      <c r="F19" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="51" t="s">
+      <c r="G19" s="50" t="s">
         <v>13</v>
       </c>
       <c r="H19" s="12" t="s">
@@ -2351,35 +2316,35 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
-      <c r="B20" s="35"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="31"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="30"/>
       <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="29">
+      <c r="A21" s="28">
         <v>8</v>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="31">
         <v>44453</v>
       </c>
-      <c r="C21" s="37">
+      <c r="C21" s="36">
         <v>2</v>
       </c>
-      <c r="D21" s="75" t="s">
+      <c r="D21" s="74" t="s">
         <v>41</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="93" t="s">
+      <c r="F21" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="51" t="s">
+      <c r="G21" s="50" t="s">
         <v>43</v>
       </c>
       <c r="H21" s="10" t="s">
@@ -2387,23 +2352,23 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="31"/>
-      <c r="B22" s="34">
+      <c r="A22" s="30"/>
+      <c r="B22" s="33">
         <v>44453</v>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="35">
         <v>1</v>
       </c>
-      <c r="D22" s="64" t="s">
+      <c r="D22" s="63" t="s">
         <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="94" t="s">
+      <c r="F22" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="59" t="s">
+      <c r="G22" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H22" s="12" t="s">
@@ -2411,35 +2376,35 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="97"/>
-      <c r="G23" s="30"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="96"/>
+      <c r="G23" s="29"/>
       <c r="H23" s="11"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="29">
-        <v>9</v>
-      </c>
-      <c r="B24" s="32">
+      <c r="A24" s="28">
+        <v>9</v>
+      </c>
+      <c r="B24" s="31">
         <v>44454</v>
       </c>
-      <c r="C24" s="37">
+      <c r="C24" s="36">
         <v>2</v>
       </c>
-      <c r="D24" s="75" t="s">
+      <c r="D24" s="74" t="s">
         <v>47</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F24" s="93" t="s">
+      <c r="F24" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="G24" s="59" t="s">
+      <c r="G24" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H24" s="3" t="s">
@@ -2447,35 +2412,35 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="30"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="98"/>
-      <c r="G25" s="36"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="97"/>
+      <c r="G25" s="35"/>
       <c r="H25" s="12"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="60">
+      <c r="A26" s="59">
         <v>10</v>
       </c>
-      <c r="B26" s="62">
+      <c r="B26" s="61">
         <v>44455</v>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="36">
         <v>3</v>
       </c>
-      <c r="D26" s="75" t="s">
+      <c r="D26" s="74" t="s">
         <v>50</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F26" s="93" t="s">
+      <c r="F26" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="51" t="s">
+      <c r="G26" s="50" t="s">
         <v>53</v>
       </c>
       <c r="H26" s="10" t="s">
@@ -2483,23 +2448,23 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="61"/>
-      <c r="B27" s="63">
+      <c r="A27" s="60"/>
+      <c r="B27" s="62">
         <v>44455</v>
       </c>
-      <c r="C27" s="36">
+      <c r="C27" s="35">
         <v>1</v>
       </c>
-      <c r="D27" s="64" t="s">
+      <c r="D27" s="63" t="s">
         <v>54</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F27" s="94" t="s">
+      <c r="F27" s="93" t="s">
         <v>55</v>
       </c>
-      <c r="G27" s="59" t="s">
+      <c r="G27" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H27" s="12" t="s">
@@ -2507,107 +2472,107 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="57"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="74"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="97"/>
-      <c r="G28" s="30"/>
+      <c r="A28" s="56"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="29"/>
       <c r="H28" s="11"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="29">
+      <c r="A29" s="28">
         <v>11</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="33">
         <v>44456</v>
       </c>
-      <c r="C29" s="36">
+      <c r="C29" s="35">
         <v>2</v>
       </c>
-      <c r="D29" s="79" t="s">
+      <c r="D29" s="78" t="s">
         <v>56</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F29" s="93" t="s">
+      <c r="F29" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="G29" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="64" t="s">
+      <c r="G29" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="63" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="30"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="74"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="96"/>
-      <c r="G30" s="35"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="11"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="29">
+      <c r="A31" s="28">
         <v>12</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="31">
         <v>44457</v>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="36">
         <v>3</v>
       </c>
-      <c r="D31" s="79" t="s">
+      <c r="D31" s="78" t="s">
         <v>59</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F31" s="93" t="s">
+      <c r="F31" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="G31" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="19" t="s">
+      <c r="G31" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="18" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="30"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="76"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="75"/>
       <c r="E32" s="5"/>
-      <c r="F32" s="95"/>
-      <c r="G32" s="35"/>
+      <c r="F32" s="94"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="11"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="29">
-        <v>13</v>
-      </c>
-      <c r="B33" s="32">
+      <c r="A33" s="28">
+        <v>13</v>
+      </c>
+      <c r="B33" s="31">
         <v>44458</v>
       </c>
-      <c r="C33" s="37">
+      <c r="C33" s="36">
         <v>1</v>
       </c>
-      <c r="D33" s="75" t="s">
+      <c r="D33" s="74" t="s">
         <v>62</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F33" s="93" t="s">
+      <c r="F33" s="92" t="s">
         <v>64</v>
       </c>
-      <c r="G33" s="59" t="s">
+      <c r="G33" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H33" s="10" t="s">
@@ -2615,35 +2580,35 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="31"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="64"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="63"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="99"/>
-      <c r="G34" s="38"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="37"/>
       <c r="H34" s="12"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="29">
+      <c r="A35" s="28">
         <v>14</v>
       </c>
-      <c r="B35" s="45">
+      <c r="B35" s="44">
         <v>44459</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="28">
         <v>2</v>
       </c>
-      <c r="D35" s="68" t="s">
+      <c r="D35" s="67" t="s">
         <v>65</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F35" s="100" t="s">
+      <c r="F35" s="99" t="s">
         <v>68</v>
       </c>
-      <c r="G35" s="51" t="s">
+      <c r="G35" s="50" t="s">
         <v>67</v>
       </c>
       <c r="H35" s="10" t="s">
@@ -2651,23 +2616,23 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="31"/>
-      <c r="B36" s="46">
+      <c r="A36" s="30"/>
+      <c r="B36" s="45">
         <v>44459</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="30">
         <v>1</v>
       </c>
-      <c r="D36" s="69" t="s">
+      <c r="D36" s="68" t="s">
         <v>69</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F36" s="94" t="s">
+      <c r="F36" s="93" t="s">
         <v>70</v>
       </c>
-      <c r="G36" s="59" t="s">
+      <c r="G36" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H36" s="12" t="s">
@@ -2675,35 +2640,35 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="30"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="78"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="96"/>
-      <c r="G37" s="30"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="29"/>
       <c r="H37" s="11"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="31">
+      <c r="A38" s="30">
         <v>15</v>
       </c>
-      <c r="B38" s="34">
+      <c r="B38" s="33">
         <v>44460</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="35">
         <v>2</v>
       </c>
-      <c r="D38" s="68" t="s">
+      <c r="D38" s="67" t="s">
         <v>71</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F38" s="100" t="s">
+      <c r="F38" s="99" t="s">
         <v>73</v>
       </c>
-      <c r="G38" s="59" t="s">
+      <c r="G38" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H38" s="12" t="s">
@@ -2711,95 +2676,95 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="30"/>
-      <c r="B39" s="35"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="96"/>
-      <c r="G39" s="35"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="95"/>
+      <c r="G39" s="34"/>
       <c r="H39" s="12"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="29">
+      <c r="A40" s="28">
         <v>16</v>
       </c>
-      <c r="B40" s="32">
+      <c r="B40" s="31">
         <v>44461</v>
       </c>
-      <c r="C40" s="37">
+      <c r="C40" s="36">
         <v>3</v>
       </c>
-      <c r="D40" s="68" t="s">
+      <c r="D40" s="67" t="s">
         <v>74</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="100" t="s">
+      <c r="F40" s="99" t="s">
         <v>77</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="H40" s="53" t="s">
+      <c r="H40" s="52" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="31"/>
-      <c r="B41" s="34">
+      <c r="A41" s="30"/>
+      <c r="B41" s="33">
         <v>44461</v>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="35">
         <v>1</v>
       </c>
-      <c r="D41" s="64" t="s">
+      <c r="D41" s="63" t="s">
         <v>78</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F41" s="94" t="s">
+      <c r="F41" s="93" t="s">
         <v>79</v>
       </c>
-      <c r="G41" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="H41" s="54" t="s">
+      <c r="G41" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="53" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="30"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="96"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="95"/>
       <c r="G42" s="4"/>
-      <c r="H42" s="55"/>
+      <c r="H42" s="54"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="29">
+      <c r="A43" s="28">
         <v>17</v>
       </c>
-      <c r="B43" s="32">
+      <c r="B43" s="31">
         <v>44462</v>
       </c>
-      <c r="C43" s="37">
+      <c r="C43" s="36">
         <v>2</v>
       </c>
-      <c r="D43" s="68" t="s">
+      <c r="D43" s="67" t="s">
         <v>80</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F43" s="100" t="s">
+      <c r="F43" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="G43" s="59" t="s">
+      <c r="G43" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H43" s="3" t="s">
@@ -2807,59 +2772,59 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="30"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="73"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="98"/>
-      <c r="G44" s="36"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="72"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="97"/>
+      <c r="G44" s="35"/>
       <c r="H44" s="12"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="60">
+      <c r="A45" s="59">
         <v>18</v>
       </c>
-      <c r="B45" s="45">
+      <c r="B45" s="44">
         <v>44463</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="28">
         <v>3</v>
       </c>
-      <c r="D45" s="68" t="s">
+      <c r="D45" s="67" t="s">
         <v>83</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F45" s="100" t="s">
+      <c r="F45" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="G45" s="51" t="s">
+      <c r="G45" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="H45" s="19" t="s">
+      <c r="H45" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="61"/>
-      <c r="B46" s="46">
+      <c r="A46" s="60"/>
+      <c r="B46" s="45">
         <v>44463</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="30">
         <v>1</v>
       </c>
-      <c r="D46" s="69" t="s">
+      <c r="D46" s="68" t="s">
         <v>87</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F46" s="94" t="s">
+      <c r="F46" s="93" t="s">
         <v>88</v>
       </c>
-      <c r="G46" s="59" t="s">
+      <c r="G46" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H46" s="3" t="s">
@@ -2867,71 +2832,71 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="57"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="78"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="96"/>
-      <c r="G47" s="30"/>
+      <c r="A47" s="56"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="95"/>
+      <c r="G47" s="29"/>
       <c r="H47" s="11"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="29">
+      <c r="A48" s="28">
         <v>19</v>
       </c>
-      <c r="B48" s="34">
+      <c r="B48" s="33">
         <v>44464</v>
       </c>
-      <c r="C48" s="36">
+      <c r="C48" s="35">
         <v>2</v>
       </c>
-      <c r="D48" s="68" t="s">
+      <c r="D48" s="67" t="s">
         <v>89</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F48" s="100" t="s">
+      <c r="F48" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="G48" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="H48" s="65" t="s">
+      <c r="G48" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="64" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="31"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="73"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="98"/>
-      <c r="G49" s="36"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="35"/>
+      <c r="C49" s="35"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="97"/>
+      <c r="G49" s="35"/>
       <c r="H49" s="12"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="29">
+      <c r="A50" s="28">
         <v>20</v>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="31">
         <v>44465</v>
       </c>
-      <c r="C50" s="37">
+      <c r="C50" s="36">
         <v>3</v>
       </c>
-      <c r="D50" s="75" t="s">
+      <c r="D50" s="74" t="s">
         <v>91</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F50" s="100" t="s">
+      <c r="F50" s="99" t="s">
         <v>93</v>
       </c>
-      <c r="G50" s="40" t="s">
+      <c r="G50" s="39" t="s">
         <v>94</v>
       </c>
       <c r="H50" s="10" t="s">
@@ -2939,23 +2904,23 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="31"/>
-      <c r="B51" s="34">
+      <c r="A51" s="30"/>
+      <c r="B51" s="33">
         <v>44465</v>
       </c>
-      <c r="C51" s="36">
+      <c r="C51" s="35">
         <v>1</v>
       </c>
-      <c r="D51" s="64" t="s">
+      <c r="D51" s="63" t="s">
         <v>95</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F51" s="94" t="s">
+      <c r="F51" s="93" t="s">
         <v>96</v>
       </c>
-      <c r="G51" s="59" t="s">
+      <c r="G51" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H51" s="12" t="s">
@@ -2963,35 +2928,35 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="30"/>
-      <c r="B52" s="35"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="74"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="96"/>
-      <c r="G52" s="35"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="95"/>
+      <c r="G52" s="34"/>
       <c r="H52" s="11"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="31">
+      <c r="A53" s="30">
         <v>21</v>
       </c>
-      <c r="B53" s="34">
+      <c r="B53" s="33">
         <v>44466</v>
       </c>
-      <c r="C53" s="36">
+      <c r="C53" s="35">
         <v>2</v>
       </c>
-      <c r="D53" s="75" t="s">
+      <c r="D53" s="74" t="s">
         <v>97</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F53" s="100" t="s">
+      <c r="F53" s="99" t="s">
         <v>99</v>
       </c>
-      <c r="G53" s="59" t="s">
+      <c r="G53" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H53" s="12" t="s">
@@ -2999,35 +2964,35 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="30"/>
-      <c r="B54" s="35"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="74"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="96"/>
-      <c r="G54" s="35"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="95"/>
+      <c r="G54" s="34"/>
       <c r="H54" s="11"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="29">
+      <c r="A55" s="28">
         <v>22</v>
       </c>
-      <c r="B55" s="32">
+      <c r="B55" s="31">
         <v>44467</v>
       </c>
-      <c r="C55" s="37">
+      <c r="C55" s="36">
         <v>1</v>
       </c>
-      <c r="D55" s="75" t="s">
+      <c r="D55" s="74" t="s">
         <v>101</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F55" s="100" t="s">
+      <c r="F55" s="99" t="s">
         <v>103</v>
       </c>
-      <c r="G55" s="59" t="s">
+      <c r="G55" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H55" s="10" t="s">
@@ -3035,35 +3000,35 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="30"/>
-      <c r="B56" s="35"/>
-      <c r="C56" s="35"/>
-      <c r="D56" s="74"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="96"/>
-      <c r="G56" s="35"/>
+      <c r="A56" s="29"/>
+      <c r="B56" s="34"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="73"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="95"/>
+      <c r="G56" s="34"/>
       <c r="H56" s="11"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="29">
+      <c r="A57" s="28">
         <v>23</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="31">
         <v>44468</v>
       </c>
-      <c r="C57" s="37">
+      <c r="C57" s="36">
         <v>2</v>
       </c>
-      <c r="D57" s="75" t="s">
+      <c r="D57" s="74" t="s">
         <v>104</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F57" s="100" t="s">
+      <c r="F57" s="99" t="s">
         <v>106</v>
       </c>
-      <c r="G57" s="59" t="s">
+      <c r="G57" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H57" s="10" t="s">
@@ -3071,35 +3036,35 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="31"/>
-      <c r="B58" s="36"/>
-      <c r="C58" s="36"/>
-      <c r="D58" s="73"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="98"/>
-      <c r="G58" s="36"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="72"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="97"/>
+      <c r="G58" s="35"/>
       <c r="H58" s="12"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="29">
+      <c r="A59" s="28">
         <v>24</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59" s="31">
         <v>44469</v>
       </c>
-      <c r="C59" s="37">
+      <c r="C59" s="36">
         <v>3</v>
       </c>
-      <c r="D59" s="68" t="s">
+      <c r="D59" s="67" t="s">
         <v>107</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F59" s="100" t="s">
+      <c r="F59" s="99" t="s">
         <v>109</v>
       </c>
-      <c r="G59" s="40" t="s">
+      <c r="G59" s="39" t="s">
         <v>110</v>
       </c>
       <c r="H59" s="10" t="s">
@@ -3107,23 +3072,23 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="31"/>
-      <c r="B60" s="34">
+      <c r="A60" s="30"/>
+      <c r="B60" s="33">
         <v>44469</v>
       </c>
-      <c r="C60" s="36">
+      <c r="C60" s="35">
         <v>1</v>
       </c>
-      <c r="D60" s="69" t="s">
+      <c r="D60" s="68" t="s">
         <v>111</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F60" s="94" t="s">
+      <c r="F60" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="G60" s="59" t="s">
+      <c r="G60" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H60" s="12" t="s">
@@ -3131,35 +3096,35 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="30"/>
-      <c r="B61" s="35"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="78"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="96"/>
-      <c r="G61" s="35"/>
+      <c r="A61" s="29"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="77"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="95"/>
+      <c r="G61" s="34"/>
       <c r="H61" s="11"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="31">
+      <c r="A62" s="30">
         <v>25</v>
       </c>
-      <c r="B62" s="34">
+      <c r="B62" s="33">
         <v>44470</v>
       </c>
-      <c r="C62" s="36">
+      <c r="C62" s="35">
         <v>2</v>
       </c>
-      <c r="D62" s="68" t="s">
+      <c r="D62" s="67" t="s">
         <v>113</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F62" s="100" t="s">
+      <c r="F62" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="G62" s="59" t="s">
+      <c r="G62" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H62" s="12" t="s">
@@ -3167,95 +3132,95 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="30"/>
-      <c r="B63" s="35"/>
-      <c r="C63" s="35"/>
-      <c r="D63" s="74"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="96"/>
-      <c r="G63" s="35"/>
+      <c r="A63" s="29"/>
+      <c r="B63" s="34"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="73"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="95"/>
+      <c r="G63" s="34"/>
       <c r="H63" s="12"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="29">
+      <c r="A64" s="28">
         <v>26</v>
       </c>
-      <c r="B64" s="32">
+      <c r="B64" s="31">
         <v>44471</v>
       </c>
-      <c r="C64" s="37">
+      <c r="C64" s="36">
         <v>3</v>
       </c>
-      <c r="D64" s="68" t="s">
+      <c r="D64" s="67" t="s">
         <v>116</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F64" s="100" t="s">
+      <c r="F64" s="99" t="s">
         <v>118</v>
       </c>
       <c r="G64" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="H64" s="53" t="s">
+      <c r="H64" s="52" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="31"/>
-      <c r="B65" s="34">
+      <c r="A65" s="30"/>
+      <c r="B65" s="33">
         <v>44471</v>
       </c>
-      <c r="C65" s="36">
+      <c r="C65" s="35">
         <v>1</v>
       </c>
-      <c r="D65" s="64" t="s">
+      <c r="D65" s="63" t="s">
         <v>120</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F65" s="94" t="s">
+      <c r="F65" s="93" t="s">
         <v>121</v>
       </c>
-      <c r="G65" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="H65" s="54" t="s">
+      <c r="G65" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H65" s="53" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="31"/>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="73"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="98"/>
+      <c r="A66" s="30"/>
+      <c r="B66" s="35"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="72"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="97"/>
       <c r="G66" s="1"/>
-      <c r="H66" s="54"/>
+      <c r="H66" s="53"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="29">
+      <c r="A67" s="28">
         <v>27</v>
       </c>
-      <c r="B67" s="32">
+      <c r="B67" s="31">
         <v>44472</v>
       </c>
-      <c r="C67" s="37">
+      <c r="C67" s="36">
         <v>2</v>
       </c>
-      <c r="D67" s="75" t="s">
+      <c r="D67" s="74" t="s">
         <v>122</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F67" s="100" t="s">
+      <c r="F67" s="99" t="s">
         <v>124</v>
       </c>
-      <c r="G67" s="40" t="s">
+      <c r="G67" s="39" t="s">
         <v>125</v>
       </c>
       <c r="H67" s="10" t="s">
@@ -3263,23 +3228,23 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="31"/>
-      <c r="B68" s="34">
+      <c r="A68" s="30"/>
+      <c r="B68" s="33">
         <v>44472</v>
       </c>
-      <c r="C68" s="36">
+      <c r="C68" s="35">
         <v>1</v>
       </c>
-      <c r="D68" s="64" t="s">
+      <c r="D68" s="63" t="s">
         <v>126</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F68" s="94" t="s">
+      <c r="F68" s="93" t="s">
         <v>127</v>
       </c>
-      <c r="G68" s="49" t="s">
+      <c r="G68" s="48" t="s">
         <v>13</v>
       </c>
       <c r="H68" s="12" t="s">
@@ -3287,35 +3252,35 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="30"/>
-      <c r="B69" s="35"/>
-      <c r="C69" s="35"/>
-      <c r="D69" s="74"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="96"/>
-      <c r="G69" s="35"/>
+      <c r="A69" s="29"/>
+      <c r="B69" s="34"/>
+      <c r="C69" s="34"/>
+      <c r="D69" s="73"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="95"/>
+      <c r="G69" s="34"/>
       <c r="H69" s="11"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="31">
+      <c r="A70" s="30">
         <v>28</v>
       </c>
-      <c r="B70" s="32">
+      <c r="B70" s="31">
         <v>44473</v>
       </c>
-      <c r="C70" s="36">
+      <c r="C70" s="35">
         <v>2</v>
       </c>
-      <c r="D70" s="75" t="s">
+      <c r="D70" s="74" t="s">
         <v>128</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F70" s="100" t="s">
+      <c r="F70" s="99" t="s">
         <v>130</v>
       </c>
-      <c r="G70" s="59" t="s">
+      <c r="G70" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H70" s="12" t="s">
@@ -3323,35 +3288,35 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="30"/>
-      <c r="B71" s="35"/>
-      <c r="C71" s="35"/>
-      <c r="D71" s="74"/>
-      <c r="E71" s="23"/>
-      <c r="F71" s="96"/>
-      <c r="G71" s="35"/>
+      <c r="A71" s="29"/>
+      <c r="B71" s="34"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="73"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="95"/>
+      <c r="G71" s="34"/>
       <c r="H71" s="11"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="29">
+      <c r="A72" s="28">
         <v>29</v>
       </c>
-      <c r="B72" s="32">
+      <c r="B72" s="31">
         <v>44474</v>
       </c>
-      <c r="C72" s="37">
+      <c r="C72" s="36">
         <v>1</v>
       </c>
-      <c r="D72" s="79" t="s">
+      <c r="D72" s="78" t="s">
         <v>131</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F72" s="100" t="s">
+      <c r="F72" s="99" t="s">
         <v>132</v>
       </c>
-      <c r="G72" s="59" t="s">
+      <c r="G72" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H72" s="10" t="s">
@@ -3359,35 +3324,35 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="31"/>
-      <c r="B73" s="36"/>
-      <c r="C73" s="36"/>
-      <c r="D73" s="73"/>
-      <c r="E73" s="16"/>
-      <c r="F73" s="98"/>
-      <c r="G73" s="36"/>
+      <c r="A73" s="30"/>
+      <c r="B73" s="35"/>
+      <c r="C73" s="35"/>
+      <c r="D73" s="72"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="97"/>
+      <c r="G73" s="35"/>
       <c r="H73" s="12"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="29">
+      <c r="A74" s="28">
         <v>30</v>
       </c>
-      <c r="B74" s="45">
+      <c r="B74" s="44">
         <v>44475</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C74" s="28">
         <v>2</v>
       </c>
-      <c r="D74" s="80" t="s">
+      <c r="D74" s="79" t="s">
         <v>134</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F74" s="100" t="s">
+      <c r="F74" s="99" t="s">
         <v>136</v>
       </c>
-      <c r="G74" s="51" t="s">
+      <c r="G74" s="50" t="s">
         <v>137</v>
       </c>
       <c r="H74" s="10" t="s">
@@ -3395,23 +3360,23 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="31"/>
-      <c r="B75" s="46">
+      <c r="A75" s="30"/>
+      <c r="B75" s="45">
         <v>44475</v>
       </c>
-      <c r="C75" s="31">
+      <c r="C75" s="30">
         <v>1</v>
       </c>
-      <c r="D75" s="81" t="s">
+      <c r="D75" s="80" t="s">
         <v>138</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F75" s="94" t="s">
+      <c r="F75" s="93" t="s">
         <v>139</v>
       </c>
-      <c r="G75" s="49" t="s">
+      <c r="G75" s="48" t="s">
         <v>13</v>
       </c>
       <c r="H75" s="12" t="s">
@@ -3419,35 +3384,35 @@
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="30"/>
-      <c r="B76" s="30"/>
-      <c r="C76" s="30"/>
-      <c r="D76" s="78"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="96"/>
-      <c r="G76" s="30"/>
+      <c r="A76" s="29"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+      <c r="D76" s="77"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="95"/>
+      <c r="G76" s="29"/>
       <c r="H76" s="11"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="31">
+      <c r="A77" s="30">
         <v>31</v>
       </c>
-      <c r="B77" s="46">
+      <c r="B77" s="45">
         <v>44476</v>
       </c>
-      <c r="C77" s="36">
+      <c r="C77" s="35">
         <v>2</v>
       </c>
-      <c r="D77" s="80" t="s">
+      <c r="D77" s="79" t="s">
         <v>140</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F77" s="100" t="s">
+      <c r="F77" s="99" t="s">
         <v>142</v>
       </c>
-      <c r="G77" s="59" t="s">
+      <c r="G77" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H77" s="12" t="s">
@@ -3455,35 +3420,35 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="31"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="73"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="98"/>
-      <c r="G78" s="36"/>
+      <c r="A78" s="30"/>
+      <c r="B78" s="35"/>
+      <c r="C78" s="35"/>
+      <c r="D78" s="72"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="97"/>
+      <c r="G78" s="35"/>
       <c r="H78" s="12"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="60">
+      <c r="A79" s="59">
         <v>32</v>
       </c>
-      <c r="B79" s="45">
+      <c r="B79" s="44">
         <v>44477</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C79" s="28">
         <v>3</v>
       </c>
-      <c r="D79" s="80" t="s">
+      <c r="D79" s="79" t="s">
         <v>143</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F79" s="100" t="s">
+      <c r="F79" s="99" t="s">
         <v>146</v>
       </c>
-      <c r="G79" s="51" t="s">
+      <c r="G79" s="50" t="s">
         <v>145</v>
       </c>
       <c r="H79" s="10" t="s">
@@ -3491,23 +3456,23 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="61"/>
-      <c r="B80" s="46">
+      <c r="A80" s="60"/>
+      <c r="B80" s="45">
         <v>44477</v>
       </c>
-      <c r="C80" s="31">
+      <c r="C80" s="30">
         <v>1</v>
       </c>
-      <c r="D80" s="81" t="s">
+      <c r="D80" s="80" t="s">
         <v>147</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F80" s="94" t="s">
+      <c r="F80" s="93" t="s">
         <v>148</v>
       </c>
-      <c r="G80" s="49" t="s">
+      <c r="G80" s="48" t="s">
         <v>13</v>
       </c>
       <c r="H80" s="12" t="s">
@@ -3515,35 +3480,35 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="57"/>
-      <c r="B81" s="30"/>
-      <c r="C81" s="30"/>
-      <c r="D81" s="78"/>
-      <c r="E81" s="23"/>
-      <c r="F81" s="96"/>
-      <c r="G81" s="30"/>
+      <c r="A81" s="56"/>
+      <c r="B81" s="29"/>
+      <c r="C81" s="29"/>
+      <c r="D81" s="77"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="95"/>
+      <c r="G81" s="29"/>
       <c r="H81" s="11"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="31">
+      <c r="A82" s="30">
         <v>33</v>
       </c>
-      <c r="B82" s="34">
+      <c r="B82" s="33">
         <v>44478</v>
       </c>
-      <c r="C82" s="36">
+      <c r="C82" s="35">
         <v>2</v>
       </c>
-      <c r="D82" s="80" t="s">
+      <c r="D82" s="79" t="s">
         <v>150</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F82" s="100" t="s">
+      <c r="F82" s="99" t="s">
         <v>151</v>
       </c>
-      <c r="G82" s="38" t="s">
+      <c r="G82" s="37" t="s">
         <v>152</v>
       </c>
       <c r="H82" s="12" t="s">
@@ -3551,23 +3516,23 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="31"/>
-      <c r="B83" s="46">
+      <c r="A83" s="30"/>
+      <c r="B83" s="45">
         <v>44478</v>
       </c>
-      <c r="C83" s="36">
+      <c r="C83" s="35">
         <v>1</v>
       </c>
-      <c r="D83" s="82" t="s">
+      <c r="D83" s="81" t="s">
         <v>153</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F83" s="94" t="s">
+      <c r="F83" s="93" t="s">
         <v>154</v>
       </c>
-      <c r="G83" s="49" t="s">
+      <c r="G83" s="48" t="s">
         <v>13</v>
       </c>
       <c r="H83" s="12" t="s">
@@ -3575,35 +3540,35 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="30"/>
-      <c r="B84" s="35"/>
-      <c r="C84" s="35"/>
-      <c r="D84" s="73"/>
-      <c r="E84" s="23"/>
-      <c r="F84" s="96"/>
-      <c r="G84" s="35"/>
+      <c r="A84" s="29"/>
+      <c r="B84" s="34"/>
+      <c r="C84" s="34"/>
+      <c r="D84" s="72"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="95"/>
+      <c r="G84" s="34"/>
       <c r="H84" s="11"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="29">
+      <c r="A85" s="28">
         <v>34</v>
       </c>
-      <c r="B85" s="66" t="s">
+      <c r="B85" s="65" t="s">
         <v>158</v>
       </c>
-      <c r="C85" s="58">
+      <c r="C85" s="57">
         <v>2</v>
       </c>
-      <c r="D85" s="80" t="s">
+      <c r="D85" s="79" t="s">
         <v>155</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F85" s="100" t="s">
+      <c r="F85" s="99" t="s">
         <v>157</v>
       </c>
-      <c r="G85" s="59" t="s">
+      <c r="G85" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H85" s="10" t="s">
@@ -3611,35 +3576,35 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="30"/>
-      <c r="B86" s="36"/>
-      <c r="C86" s="36"/>
-      <c r="D86" s="73"/>
-      <c r="E86" s="16"/>
-      <c r="F86" s="98"/>
-      <c r="G86" s="36"/>
+      <c r="A86" s="29"/>
+      <c r="B86" s="35"/>
+      <c r="C86" s="35"/>
+      <c r="D86" s="72"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="97"/>
+      <c r="G86" s="35"/>
       <c r="H86" s="12"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="60">
+      <c r="A87" s="59">
         <v>35</v>
       </c>
-      <c r="B87" s="45">
+      <c r="B87" s="44">
         <v>44480</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C87" s="28">
         <v>3</v>
       </c>
-      <c r="D87" s="79" t="s">
+      <c r="D87" s="78" t="s">
         <v>159</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F87" s="100" t="s">
+      <c r="F87" s="99" t="s">
         <v>161</v>
       </c>
-      <c r="G87" s="51" t="s">
+      <c r="G87" s="50" t="s">
         <v>162</v>
       </c>
       <c r="H87" s="10" t="s">
@@ -3647,59 +3612,59 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="61"/>
-      <c r="B88" s="46">
+      <c r="A88" s="60"/>
+      <c r="B88" s="45">
         <v>44480</v>
       </c>
-      <c r="C88" s="31">
+      <c r="C88" s="30">
         <v>1</v>
       </c>
-      <c r="D88" s="82" t="s">
+      <c r="D88" s="81" t="s">
         <v>163</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F88" s="94" t="s">
+      <c r="F88" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="G88" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="H88" s="67" t="s">
+      <c r="G88" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H88" s="66" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="57"/>
-      <c r="B89" s="30"/>
-      <c r="C89" s="30"/>
-      <c r="D89" s="74"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="96"/>
-      <c r="G89" s="30"/>
+      <c r="A89" s="56"/>
+      <c r="B89" s="29"/>
+      <c r="C89" s="29"/>
+      <c r="D89" s="73"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="95"/>
+      <c r="G89" s="29"/>
       <c r="H89" s="11"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="29">
+      <c r="A90" s="28">
         <v>36</v>
       </c>
-      <c r="B90" s="34">
+      <c r="B90" s="33">
         <v>44481</v>
       </c>
-      <c r="C90" s="36">
+      <c r="C90" s="35">
         <v>2</v>
       </c>
-      <c r="D90" s="82" t="s">
+      <c r="D90" s="81" t="s">
         <v>165</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F90" s="100" t="s">
+      <c r="F90" s="99" t="s">
         <v>167</v>
       </c>
-      <c r="G90" s="38" t="s">
+      <c r="G90" s="37" t="s">
         <v>166</v>
       </c>
       <c r="H90" s="12" t="s">
@@ -3707,23 +3672,23 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="31"/>
-      <c r="B91" s="34">
+      <c r="A91" s="30"/>
+      <c r="B91" s="33">
         <v>44481</v>
       </c>
-      <c r="C91" s="36">
+      <c r="C91" s="35">
         <v>1</v>
       </c>
-      <c r="D91" s="64" t="s">
+      <c r="D91" s="63" t="s">
         <v>169</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F91" s="94" t="s">
+      <c r="F91" s="93" t="s">
         <v>170</v>
       </c>
-      <c r="G91" s="59" t="s">
+      <c r="G91" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H91" s="12" t="s">
@@ -3731,35 +3696,35 @@
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="30"/>
-      <c r="B92" s="35"/>
-      <c r="C92" s="35"/>
-      <c r="D92" s="74"/>
-      <c r="E92" s="23"/>
-      <c r="F92" s="96"/>
-      <c r="G92" s="35"/>
+      <c r="A92" s="29"/>
+      <c r="B92" s="34"/>
+      <c r="C92" s="34"/>
+      <c r="D92" s="73"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="95"/>
+      <c r="G92" s="34"/>
       <c r="H92" s="11"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="29">
+      <c r="A93" s="28">
         <v>37</v>
       </c>
-      <c r="B93" s="32">
+      <c r="B93" s="31">
         <v>44482</v>
       </c>
-      <c r="C93" s="37">
+      <c r="C93" s="36">
         <v>2</v>
       </c>
-      <c r="D93" s="82" t="s">
+      <c r="D93" s="81" t="s">
         <v>171</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F93" s="100" t="s">
+      <c r="F93" s="99" t="s">
         <v>173</v>
       </c>
-      <c r="G93" s="59" t="s">
+      <c r="G93" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H93" s="10" t="s">
@@ -3767,95 +3732,95 @@
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="30"/>
-      <c r="B94" s="35"/>
-      <c r="C94" s="35"/>
-      <c r="D94" s="74"/>
-      <c r="E94" s="23"/>
-      <c r="F94" s="96"/>
-      <c r="G94" s="35"/>
+      <c r="A94" s="29"/>
+      <c r="B94" s="34"/>
+      <c r="C94" s="34"/>
+      <c r="D94" s="73"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="95"/>
+      <c r="G94" s="34"/>
       <c r="H94" s="11"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="31">
+      <c r="A95" s="30">
         <v>38</v>
       </c>
-      <c r="B95" s="34">
+      <c r="B95" s="33">
         <v>44483</v>
       </c>
-      <c r="C95" s="36">
+      <c r="C95" s="35">
         <v>3</v>
       </c>
-      <c r="D95" s="80" t="s">
+      <c r="D95" s="79" t="s">
         <v>174</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F95" s="100" t="s">
+      <c r="F95" s="99" t="s">
         <v>177</v>
       </c>
-      <c r="G95" s="51" t="s">
+      <c r="G95" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="H95" s="53" t="s">
+      <c r="H95" s="52" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="31"/>
-      <c r="B96" s="34">
+      <c r="A96" s="30"/>
+      <c r="B96" s="33">
         <v>44483</v>
       </c>
-      <c r="C96" s="36">
+      <c r="C96" s="35">
         <v>1</v>
       </c>
-      <c r="D96" s="69" t="s">
+      <c r="D96" s="68" t="s">
         <v>178</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F96" s="99" t="s">
+      <c r="F96" s="98" t="s">
         <v>179</v>
       </c>
-      <c r="G96" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="H96" s="54" t="s">
+      <c r="G96" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H96" s="53" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="31"/>
-      <c r="B97" s="36"/>
-      <c r="C97" s="36"/>
-      <c r="D97" s="78"/>
-      <c r="E97" s="23"/>
-      <c r="F97" s="96"/>
-      <c r="G97" s="30"/>
-      <c r="H97" s="55"/>
+      <c r="A97" s="30"/>
+      <c r="B97" s="35"/>
+      <c r="C97" s="35"/>
+      <c r="D97" s="77"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="95"/>
+      <c r="G97" s="29"/>
+      <c r="H97" s="54"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="29">
+      <c r="A98" s="28">
         <v>39</v>
       </c>
-      <c r="B98" s="32">
+      <c r="B98" s="31">
         <v>44484</v>
       </c>
-      <c r="C98" s="37">
+      <c r="C98" s="36">
         <v>2</v>
       </c>
-      <c r="D98" s="82" t="s">
+      <c r="D98" s="81" t="s">
         <v>180</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F98" s="100" t="s">
+      <c r="F98" s="99" t="s">
         <v>182</v>
       </c>
-      <c r="G98" s="59" t="s">
+      <c r="G98" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H98" s="10" t="s">
@@ -3863,35 +3828,35 @@
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="30"/>
-      <c r="B99" s="33"/>
-      <c r="C99" s="35"/>
-      <c r="D99" s="76"/>
+      <c r="A99" s="29"/>
+      <c r="B99" s="32"/>
+      <c r="C99" s="34"/>
+      <c r="D99" s="75"/>
       <c r="E99" s="5"/>
-      <c r="F99" s="95"/>
-      <c r="G99" s="39"/>
+      <c r="F99" s="94"/>
+      <c r="G99" s="38"/>
       <c r="H99" s="11"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="29">
+      <c r="A100" s="28">
         <v>40</v>
       </c>
-      <c r="B100" s="32">
+      <c r="B100" s="31">
         <v>44485</v>
       </c>
-      <c r="C100" s="37">
+      <c r="C100" s="36">
         <v>1</v>
       </c>
-      <c r="D100" s="75" t="s">
+      <c r="D100" s="74" t="s">
         <v>183</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F100" s="100" t="s">
+      <c r="F100" s="99" t="s">
         <v>185</v>
       </c>
-      <c r="G100" s="40" t="s">
+      <c r="G100" s="39" t="s">
         <v>184</v>
       </c>
       <c r="H100" s="10" t="s">
@@ -3899,23 +3864,23 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="31"/>
-      <c r="B101" s="34">
+      <c r="A101" s="30"/>
+      <c r="B101" s="33">
         <v>44485</v>
       </c>
-      <c r="C101" s="36">
+      <c r="C101" s="35">
         <v>1</v>
       </c>
-      <c r="D101" s="64" t="s">
+      <c r="D101" s="63" t="s">
         <v>187</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F101" s="99" t="s">
+      <c r="F101" s="98" t="s">
         <v>188</v>
       </c>
-      <c r="G101" s="59" t="s">
+      <c r="G101" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H101" s="12" t="s">
@@ -3923,35 +3888,35 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="30"/>
-      <c r="B102" s="33"/>
-      <c r="C102" s="35"/>
-      <c r="D102" s="76"/>
+      <c r="A102" s="29"/>
+      <c r="B102" s="32"/>
+      <c r="C102" s="34"/>
+      <c r="D102" s="75"/>
       <c r="E102" s="5"/>
-      <c r="F102" s="95"/>
-      <c r="G102" s="39"/>
+      <c r="F102" s="94"/>
+      <c r="G102" s="38"/>
       <c r="H102" s="11"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="29">
+      <c r="A103" s="28">
         <v>41</v>
       </c>
-      <c r="B103" s="32">
+      <c r="B103" s="31">
         <v>44486</v>
       </c>
-      <c r="C103" s="37">
+      <c r="C103" s="36">
         <v>2</v>
       </c>
-      <c r="D103" s="75" t="s">
+      <c r="D103" s="74" t="s">
         <v>189</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F103" s="100" t="s">
+      <c r="F103" s="99" t="s">
         <v>191</v>
       </c>
-      <c r="G103" s="59" t="s">
+      <c r="G103" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H103" s="10" t="s">
@@ -3959,95 +3924,95 @@
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="30"/>
-      <c r="B104" s="33"/>
-      <c r="C104" s="35"/>
-      <c r="D104" s="76"/>
+      <c r="A104" s="29"/>
+      <c r="B104" s="32"/>
+      <c r="C104" s="34"/>
+      <c r="D104" s="75"/>
       <c r="E104" s="5"/>
-      <c r="F104" s="95"/>
-      <c r="G104" s="39"/>
+      <c r="F104" s="94"/>
+      <c r="G104" s="38"/>
       <c r="H104" s="12"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="29">
+      <c r="A105" s="28">
         <v>42</v>
       </c>
-      <c r="B105" s="32">
+      <c r="B105" s="31">
         <v>44487</v>
       </c>
-      <c r="C105" s="37">
+      <c r="C105" s="36">
         <v>3</v>
       </c>
-      <c r="D105" s="75" t="s">
+      <c r="D105" s="74" t="s">
         <v>192</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F105" s="100" t="s">
+      <c r="F105" s="99" t="s">
         <v>195</v>
       </c>
       <c r="G105" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="H105" s="53" t="s">
+      <c r="H105" s="52" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="31"/>
-      <c r="B106" s="34">
+      <c r="A106" s="30"/>
+      <c r="B106" s="33">
         <v>44487</v>
       </c>
-      <c r="C106" s="36">
+      <c r="C106" s="35">
         <v>1</v>
       </c>
-      <c r="D106" s="64" t="s">
+      <c r="D106" s="63" t="s">
         <v>196</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F106" s="99" t="s">
+      <c r="F106" s="98" t="s">
         <v>197</v>
       </c>
-      <c r="G106" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="H106" s="54" t="s">
+      <c r="G106" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H106" s="53" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="30"/>
-      <c r="B107" s="33"/>
-      <c r="C107" s="35"/>
-      <c r="D107" s="76"/>
+      <c r="A107" s="29"/>
+      <c r="B107" s="32"/>
+      <c r="C107" s="34"/>
+      <c r="D107" s="75"/>
       <c r="E107" s="5"/>
-      <c r="F107" s="95"/>
+      <c r="F107" s="94"/>
       <c r="G107" s="6"/>
-      <c r="H107" s="55"/>
+      <c r="H107" s="54"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="29">
+      <c r="A108" s="28">
         <v>43</v>
       </c>
-      <c r="B108" s="32">
+      <c r="B108" s="31">
         <v>44488</v>
       </c>
-      <c r="C108" s="37">
+      <c r="C108" s="36">
         <v>2</v>
       </c>
-      <c r="D108" s="75" t="s">
+      <c r="D108" s="74" t="s">
         <v>198</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F108" s="100" t="s">
+      <c r="F108" s="99" t="s">
         <v>200</v>
       </c>
-      <c r="G108" s="40" t="s">
+      <c r="G108" s="39" t="s">
         <v>201</v>
       </c>
       <c r="H108" s="12" t="s">
@@ -4055,23 +4020,23 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="31"/>
-      <c r="B109" s="34">
+      <c r="A109" s="30"/>
+      <c r="B109" s="33">
         <v>44488</v>
       </c>
-      <c r="C109" s="36">
+      <c r="C109" s="35">
         <v>1</v>
       </c>
-      <c r="D109" s="64" t="s">
+      <c r="D109" s="63" t="s">
         <v>202</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F109" s="99" t="s">
+      <c r="F109" s="98" t="s">
         <v>203</v>
       </c>
-      <c r="G109" s="59" t="s">
+      <c r="G109" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H109" s="12" t="s">
@@ -4079,35 +4044,35 @@
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="30"/>
-      <c r="B110" s="33"/>
-      <c r="C110" s="35"/>
-      <c r="D110" s="76"/>
+      <c r="A110" s="29"/>
+      <c r="B110" s="32"/>
+      <c r="C110" s="34"/>
+      <c r="D110" s="75"/>
       <c r="E110" s="5"/>
-      <c r="F110" s="95"/>
-      <c r="G110" s="39"/>
+      <c r="F110" s="94"/>
+      <c r="G110" s="38"/>
       <c r="H110" s="11"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="29">
+      <c r="A111" s="28">
         <v>44</v>
       </c>
-      <c r="B111" s="32">
+      <c r="B111" s="31">
         <v>44489</v>
       </c>
-      <c r="C111" s="37">
+      <c r="C111" s="36">
         <v>2</v>
       </c>
-      <c r="D111" s="75" t="s">
+      <c r="D111" s="74" t="s">
         <v>204</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F111" s="100" t="s">
+      <c r="F111" s="99" t="s">
         <v>206</v>
       </c>
-      <c r="G111" s="59" t="s">
+      <c r="G111" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H111" s="10" t="s">
@@ -4115,35 +4080,35 @@
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="30"/>
-      <c r="B112" s="34"/>
-      <c r="C112" s="36"/>
-      <c r="D112" s="64"/>
+      <c r="A112" s="29"/>
+      <c r="B112" s="33"/>
+      <c r="C112" s="35"/>
+      <c r="D112" s="63"/>
       <c r="E112" s="2"/>
-      <c r="F112" s="99"/>
-      <c r="G112" s="38"/>
+      <c r="F112" s="98"/>
+      <c r="G112" s="37"/>
       <c r="H112" s="12"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="60">
+      <c r="A113" s="59">
         <v>45</v>
       </c>
-      <c r="B113" s="45">
+      <c r="B113" s="44">
         <v>44490</v>
       </c>
-      <c r="C113" s="37">
+      <c r="C113" s="36">
         <v>3</v>
       </c>
-      <c r="D113" s="75" t="s">
+      <c r="D113" s="74" t="s">
         <v>207</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F113" s="100" t="s">
+      <c r="F113" s="99" t="s">
         <v>210</v>
       </c>
-      <c r="G113" s="51" t="s">
+      <c r="G113" s="50" t="s">
         <v>208</v>
       </c>
       <c r="H113" s="10" t="s">
@@ -4151,23 +4116,23 @@
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="61"/>
-      <c r="B114" s="46">
+      <c r="A114" s="60"/>
+      <c r="B114" s="45">
         <v>44490</v>
       </c>
-      <c r="C114" s="36">
+      <c r="C114" s="35">
         <v>1</v>
       </c>
-      <c r="D114" s="64" t="s">
+      <c r="D114" s="63" t="s">
         <v>211</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F114" s="99" t="s">
+      <c r="F114" s="98" t="s">
         <v>212</v>
       </c>
-      <c r="G114" s="59" t="s">
+      <c r="G114" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H114" s="12" t="s">
@@ -4175,35 +4140,35 @@
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="57"/>
-      <c r="B115" s="47"/>
-      <c r="C115" s="35"/>
-      <c r="D115" s="76"/>
+      <c r="A115" s="56"/>
+      <c r="B115" s="46"/>
+      <c r="C115" s="34"/>
+      <c r="D115" s="75"/>
       <c r="E115" s="5"/>
-      <c r="F115" s="95"/>
-      <c r="G115" s="52"/>
+      <c r="F115" s="94"/>
+      <c r="G115" s="51"/>
       <c r="H115" s="11"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="29">
+      <c r="A116" s="28">
         <v>46</v>
       </c>
-      <c r="B116" s="34">
+      <c r="B116" s="33">
         <v>44491</v>
       </c>
-      <c r="C116" s="36">
+      <c r="C116" s="35">
         <v>2</v>
       </c>
-      <c r="D116" s="75" t="s">
+      <c r="D116" s="74" t="s">
         <v>213</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F116" s="100" t="s">
+      <c r="F116" s="99" t="s">
         <v>215</v>
       </c>
-      <c r="G116" s="59" t="s">
+      <c r="G116" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H116" s="12" t="s">
@@ -4211,35 +4176,35 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="30"/>
-      <c r="B117" s="33"/>
-      <c r="C117" s="35"/>
-      <c r="D117" s="76"/>
+      <c r="A117" s="29"/>
+      <c r="B117" s="32"/>
+      <c r="C117" s="34"/>
+      <c r="D117" s="75"/>
       <c r="E117" s="5"/>
-      <c r="F117" s="95"/>
-      <c r="G117" s="39"/>
+      <c r="F117" s="94"/>
+      <c r="G117" s="38"/>
       <c r="H117" s="11"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="29">
+      <c r="A118" s="28">
         <v>47</v>
       </c>
-      <c r="B118" s="32">
+      <c r="B118" s="31">
         <v>44492</v>
       </c>
-      <c r="C118" s="37">
+      <c r="C118" s="36">
         <v>3</v>
       </c>
-      <c r="D118" s="75" t="s">
+      <c r="D118" s="74" t="s">
         <v>216</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F118" s="100" t="s">
+      <c r="F118" s="99" t="s">
         <v>218</v>
       </c>
-      <c r="G118" s="59" t="s">
+      <c r="G118" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H118" s="10" t="s">
@@ -4247,35 +4212,35 @@
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="30"/>
-      <c r="B119" s="34"/>
-      <c r="C119" s="36"/>
-      <c r="D119" s="64"/>
+      <c r="A119" s="29"/>
+      <c r="B119" s="33"/>
+      <c r="C119" s="35"/>
+      <c r="D119" s="63"/>
       <c r="E119" s="2"/>
-      <c r="F119" s="99"/>
-      <c r="G119" s="38"/>
+      <c r="F119" s="98"/>
+      <c r="G119" s="37"/>
       <c r="H119" s="12"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="60">
+      <c r="A120" s="59">
         <v>48</v>
       </c>
-      <c r="B120" s="45">
+      <c r="B120" s="44">
         <v>44493</v>
       </c>
-      <c r="C120" s="37">
+      <c r="C120" s="36">
         <v>4</v>
       </c>
-      <c r="D120" s="75" t="s">
+      <c r="D120" s="74" t="s">
         <v>219</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F120" s="100" t="s">
+      <c r="F120" s="99" t="s">
         <v>222</v>
       </c>
-      <c r="G120" s="40" t="s">
+      <c r="G120" s="39" t="s">
         <v>221</v>
       </c>
       <c r="H120" s="10" t="s">
@@ -4283,23 +4248,23 @@
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="61"/>
-      <c r="B121" s="46">
+      <c r="A121" s="60"/>
+      <c r="B121" s="45">
         <v>44493</v>
       </c>
-      <c r="C121" s="36">
+      <c r="C121" s="35">
         <v>1</v>
       </c>
-      <c r="D121" s="64" t="s">
+      <c r="D121" s="63" t="s">
         <v>223</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F121" s="99" t="s">
+      <c r="F121" s="98" t="s">
         <v>224</v>
       </c>
-      <c r="G121" s="38" t="s">
+      <c r="G121" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H121" s="12" t="s">
@@ -4307,35 +4272,35 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="57"/>
-      <c r="B122" s="47"/>
-      <c r="C122" s="35"/>
-      <c r="D122" s="76"/>
+      <c r="A122" s="56"/>
+      <c r="B122" s="46"/>
+      <c r="C122" s="34"/>
+      <c r="D122" s="75"/>
       <c r="E122" s="5"/>
-      <c r="F122" s="95"/>
-      <c r="G122" s="39"/>
+      <c r="F122" s="94"/>
+      <c r="G122" s="38"/>
       <c r="H122" s="11"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="29">
+      <c r="A123" s="28">
         <v>49</v>
       </c>
-      <c r="B123" s="34">
+      <c r="B123" s="33">
         <v>44494</v>
       </c>
-      <c r="C123" s="36">
+      <c r="C123" s="35">
         <v>2</v>
       </c>
-      <c r="D123" s="75" t="s">
+      <c r="D123" s="74" t="s">
         <v>225</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F123" s="100" t="s">
+      <c r="F123" s="99" t="s">
         <v>227</v>
       </c>
-      <c r="G123" s="59" t="s">
+      <c r="G123" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H123" s="12" t="s">
@@ -4343,35 +4308,35 @@
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="30"/>
-      <c r="B124" s="34"/>
-      <c r="C124" s="36"/>
-      <c r="D124" s="64"/>
+      <c r="A124" s="29"/>
+      <c r="B124" s="33"/>
+      <c r="C124" s="35"/>
+      <c r="D124" s="63"/>
       <c r="E124" s="2"/>
-      <c r="F124" s="99"/>
-      <c r="G124" s="38"/>
+      <c r="F124" s="98"/>
+      <c r="G124" s="37"/>
       <c r="H124" s="12"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="60">
+      <c r="A125" s="59">
         <v>50</v>
       </c>
-      <c r="B125" s="45">
+      <c r="B125" s="44">
         <v>44495</v>
       </c>
-      <c r="C125" s="29">
+      <c r="C125" s="28">
         <v>3</v>
       </c>
-      <c r="D125" s="68" t="s">
+      <c r="D125" s="67" t="s">
         <v>228</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F125" s="100" t="s">
+      <c r="F125" s="99" t="s">
         <v>231</v>
       </c>
-      <c r="G125" s="40" t="s">
+      <c r="G125" s="39" t="s">
         <v>230</v>
       </c>
       <c r="H125" s="10" t="s">
@@ -4379,23 +4344,23 @@
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="61"/>
-      <c r="B126" s="46">
+      <c r="A126" s="60"/>
+      <c r="B126" s="45">
         <v>44495</v>
       </c>
-      <c r="C126" s="31">
+      <c r="C126" s="30">
         <v>1</v>
       </c>
-      <c r="D126" s="69" t="s">
+      <c r="D126" s="68" t="s">
         <v>232</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F126" s="99" t="s">
+      <c r="F126" s="98" t="s">
         <v>233</v>
       </c>
-      <c r="G126" s="38" t="s">
+      <c r="G126" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H126" s="12" t="s">
@@ -4403,35 +4368,35 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="61"/>
-      <c r="B127" s="47"/>
-      <c r="C127" s="30"/>
-      <c r="D127" s="83"/>
+      <c r="A127" s="60"/>
+      <c r="B127" s="46"/>
+      <c r="C127" s="29"/>
+      <c r="D127" s="82"/>
       <c r="E127" s="5"/>
-      <c r="F127" s="95"/>
-      <c r="G127" s="39"/>
+      <c r="F127" s="94"/>
+      <c r="G127" s="38"/>
       <c r="H127" s="11"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="29">
+      <c r="A128" s="28">
         <v>51</v>
       </c>
-      <c r="B128" s="34">
+      <c r="B128" s="33">
         <v>44496</v>
       </c>
-      <c r="C128" s="36">
+      <c r="C128" s="35">
         <v>2</v>
       </c>
-      <c r="D128" s="68" t="s">
+      <c r="D128" s="67" t="s">
         <v>234</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F128" s="100" t="s">
+      <c r="F128" s="99" t="s">
         <v>236</v>
       </c>
-      <c r="G128" s="51" t="s">
+      <c r="G128" s="50" t="s">
         <v>13</v>
       </c>
       <c r="H128" s="12" t="s">
@@ -4439,35 +4404,35 @@
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="31"/>
-      <c r="B129" s="34"/>
-      <c r="C129" s="36"/>
-      <c r="D129" s="64"/>
+      <c r="A129" s="30"/>
+      <c r="B129" s="33"/>
+      <c r="C129" s="35"/>
+      <c r="D129" s="63"/>
       <c r="E129" s="2"/>
-      <c r="F129" s="99"/>
-      <c r="G129" s="52"/>
+      <c r="F129" s="98"/>
+      <c r="G129" s="51"/>
       <c r="H129" s="12"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="29">
+      <c r="A130" s="28">
         <v>52</v>
       </c>
-      <c r="B130" s="45">
+      <c r="B130" s="44">
         <v>44497</v>
       </c>
-      <c r="C130" s="37">
+      <c r="C130" s="36">
         <v>3</v>
       </c>
-      <c r="D130" s="68" t="s">
+      <c r="D130" s="67" t="s">
         <v>237</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F130" s="100" t="s">
+      <c r="F130" s="99" t="s">
         <v>239</v>
       </c>
-      <c r="G130" s="59" t="s">
+      <c r="G130" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H130" s="10" t="s">
@@ -4475,35 +4440,35 @@
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="30"/>
-      <c r="B131" s="47"/>
-      <c r="C131" s="35"/>
-      <c r="D131" s="83"/>
+      <c r="A131" s="29"/>
+      <c r="B131" s="46"/>
+      <c r="C131" s="34"/>
+      <c r="D131" s="82"/>
       <c r="E131" s="5"/>
-      <c r="F131" s="95"/>
-      <c r="G131" s="39"/>
+      <c r="F131" s="94"/>
+      <c r="G131" s="38"/>
       <c r="H131" s="11"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="29">
+      <c r="A132" s="28">
         <v>53</v>
       </c>
-      <c r="B132" s="45">
+      <c r="B132" s="44">
         <v>44498</v>
       </c>
-      <c r="C132" s="37">
+      <c r="C132" s="36">
         <v>1</v>
       </c>
-      <c r="D132" s="68" t="s">
+      <c r="D132" s="67" t="s">
         <v>240</v>
       </c>
       <c r="E132" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F132" s="100" t="s">
+      <c r="F132" s="99" t="s">
         <v>242</v>
       </c>
-      <c r="G132" s="59" t="s">
+      <c r="G132" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H132" s="10" t="s">
@@ -4511,35 +4476,35 @@
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="30"/>
-      <c r="B133" s="47"/>
-      <c r="C133" s="35"/>
-      <c r="D133" s="83"/>
+      <c r="A133" s="29"/>
+      <c r="B133" s="46"/>
+      <c r="C133" s="34"/>
+      <c r="D133" s="82"/>
       <c r="E133" s="5"/>
-      <c r="F133" s="95"/>
-      <c r="G133" s="39"/>
+      <c r="F133" s="94"/>
+      <c r="G133" s="38"/>
       <c r="H133" s="11"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="29">
+      <c r="A134" s="28">
         <v>54</v>
       </c>
-      <c r="B134" s="45">
+      <c r="B134" s="44">
         <v>44499</v>
       </c>
-      <c r="C134" s="37">
+      <c r="C134" s="36">
         <v>2</v>
       </c>
-      <c r="D134" s="68" t="s">
+      <c r="D134" s="67" t="s">
         <v>243</v>
       </c>
       <c r="E134" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F134" s="100" t="s">
+      <c r="F134" s="99" t="s">
         <v>244</v>
       </c>
-      <c r="G134" s="59" t="s">
+      <c r="G134" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H134" s="10" t="s">
@@ -4547,35 +4512,35 @@
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="31"/>
-      <c r="B135" s="46"/>
-      <c r="C135" s="36"/>
-      <c r="D135" s="69"/>
+      <c r="A135" s="30"/>
+      <c r="B135" s="45"/>
+      <c r="C135" s="35"/>
+      <c r="D135" s="68"/>
       <c r="E135" s="2"/>
-      <c r="F135" s="99"/>
-      <c r="G135" s="38"/>
+      <c r="F135" s="98"/>
+      <c r="G135" s="37"/>
       <c r="H135" s="12"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="29">
+      <c r="A136" s="28">
         <v>55</v>
       </c>
-      <c r="B136" s="32">
+      <c r="B136" s="31">
         <v>44500</v>
       </c>
-      <c r="C136" s="37">
+      <c r="C136" s="36">
         <v>3</v>
       </c>
-      <c r="D136" s="75" t="s">
+      <c r="D136" s="74" t="s">
         <v>246</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F136" s="100" t="s">
+      <c r="F136" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="G136" s="40" t="s">
+      <c r="G136" s="39" t="s">
         <v>249</v>
       </c>
       <c r="H136" s="10" t="s">
@@ -4583,23 +4548,23 @@
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="31"/>
-      <c r="B137" s="34">
+      <c r="A137" s="30"/>
+      <c r="B137" s="33">
         <v>44500</v>
       </c>
-      <c r="C137" s="36">
+      <c r="C137" s="35">
         <v>1</v>
       </c>
-      <c r="D137" s="64" t="s">
+      <c r="D137" s="63" t="s">
         <v>250</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F137" s="99" t="s">
+      <c r="F137" s="98" t="s">
         <v>251</v>
       </c>
-      <c r="G137" s="38" t="s">
+      <c r="G137" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H137" s="12" t="s">
@@ -4607,35 +4572,35 @@
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="30"/>
-      <c r="B138" s="33"/>
-      <c r="C138" s="35"/>
-      <c r="D138" s="76"/>
+      <c r="A138" s="29"/>
+      <c r="B138" s="32"/>
+      <c r="C138" s="34"/>
+      <c r="D138" s="75"/>
       <c r="E138" s="5"/>
-      <c r="F138" s="95"/>
-      <c r="G138" s="39"/>
+      <c r="F138" s="94"/>
+      <c r="G138" s="38"/>
       <c r="H138" s="11"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="31">
+      <c r="A139" s="30">
         <v>56</v>
       </c>
-      <c r="B139" s="46">
+      <c r="B139" s="45">
         <v>44501</v>
       </c>
-      <c r="C139" s="36">
+      <c r="C139" s="35">
         <v>2</v>
       </c>
-      <c r="D139" s="75" t="s">
+      <c r="D139" s="74" t="s">
         <v>252</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F139" s="100" t="s">
+      <c r="F139" s="99" t="s">
         <v>254</v>
       </c>
-      <c r="G139" s="59" t="s">
+      <c r="G139" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H139" s="12" t="s">
@@ -4643,35 +4608,35 @@
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="31"/>
-      <c r="B140" s="46"/>
-      <c r="C140" s="36"/>
-      <c r="D140" s="69"/>
+      <c r="A140" s="30"/>
+      <c r="B140" s="45"/>
+      <c r="C140" s="35"/>
+      <c r="D140" s="68"/>
       <c r="E140" s="2"/>
-      <c r="F140" s="99"/>
-      <c r="G140" s="38"/>
+      <c r="F140" s="98"/>
+      <c r="G140" s="37"/>
       <c r="H140" s="12"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="29">
+      <c r="A141" s="28">
         <v>57</v>
       </c>
-      <c r="B141" s="32">
+      <c r="B141" s="31">
         <v>44502</v>
       </c>
-      <c r="C141" s="37">
+      <c r="C141" s="36">
         <v>3</v>
       </c>
-      <c r="D141" s="84" t="s">
+      <c r="D141" s="83" t="s">
         <v>255</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F141" s="100" t="s">
+      <c r="F141" s="99" t="s">
         <v>257</v>
       </c>
-      <c r="G141" s="40" t="s">
+      <c r="G141" s="39" t="s">
         <v>258</v>
       </c>
       <c r="H141" s="10" t="s">
@@ -4679,23 +4644,23 @@
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="31"/>
-      <c r="B142" s="34">
+      <c r="A142" s="30"/>
+      <c r="B142" s="33">
         <v>44502</v>
       </c>
-      <c r="C142" s="36">
+      <c r="C142" s="35">
         <v>1</v>
       </c>
-      <c r="D142" s="85" t="s">
+      <c r="D142" s="84" t="s">
         <v>259</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F142" s="99" t="s">
+      <c r="F142" s="98" t="s">
         <v>260</v>
       </c>
-      <c r="G142" s="38" t="s">
+      <c r="G142" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H142" s="12" t="s">
@@ -4703,35 +4668,35 @@
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="30"/>
-      <c r="B143" s="33"/>
-      <c r="C143" s="35"/>
-      <c r="D143" s="76"/>
+      <c r="A143" s="29"/>
+      <c r="B143" s="32"/>
+      <c r="C143" s="34"/>
+      <c r="D143" s="75"/>
       <c r="E143" s="5"/>
-      <c r="F143" s="95"/>
-      <c r="G143" s="39"/>
+      <c r="F143" s="94"/>
+      <c r="G143" s="38"/>
       <c r="H143" s="11"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="31">
+      <c r="A144" s="30">
         <v>58</v>
       </c>
-      <c r="B144" s="46">
+      <c r="B144" s="45">
         <v>44503</v>
       </c>
-      <c r="C144" s="36">
+      <c r="C144" s="35">
         <v>2</v>
       </c>
-      <c r="D144" s="84" t="s">
+      <c r="D144" s="83" t="s">
         <v>261</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F144" s="100" t="s">
+      <c r="F144" s="99" t="s">
         <v>263</v>
       </c>
-      <c r="G144" s="59" t="s">
+      <c r="G144" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H144" s="12" t="s">
@@ -4739,35 +4704,35 @@
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="30"/>
-      <c r="B145" s="47"/>
-      <c r="C145" s="35"/>
-      <c r="D145" s="83"/>
+      <c r="A145" s="29"/>
+      <c r="B145" s="46"/>
+      <c r="C145" s="34"/>
+      <c r="D145" s="82"/>
       <c r="E145" s="5"/>
-      <c r="F145" s="95"/>
-      <c r="G145" s="39"/>
+      <c r="F145" s="94"/>
+      <c r="G145" s="38"/>
       <c r="H145" s="11"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="29">
+      <c r="A146" s="28">
         <v>59</v>
       </c>
-      <c r="B146" s="45">
+      <c r="B146" s="44">
         <v>44504</v>
       </c>
-      <c r="C146" s="37">
+      <c r="C146" s="36">
         <v>3</v>
       </c>
-      <c r="D146" s="84" t="s">
+      <c r="D146" s="83" t="s">
         <v>264</v>
       </c>
       <c r="E146" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F146" s="100" t="s">
+      <c r="F146" s="99" t="s">
         <v>265</v>
       </c>
-      <c r="G146" s="59" t="s">
+      <c r="G146" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H146" s="10" t="s">
@@ -4775,35 +4740,35 @@
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="31"/>
-      <c r="B147" s="46"/>
-      <c r="C147" s="36"/>
-      <c r="D147" s="69"/>
+      <c r="A147" s="30"/>
+      <c r="B147" s="45"/>
+      <c r="C147" s="35"/>
+      <c r="D147" s="68"/>
       <c r="E147" s="2"/>
-      <c r="F147" s="99"/>
-      <c r="G147" s="38"/>
+      <c r="F147" s="98"/>
+      <c r="G147" s="37"/>
       <c r="H147" s="12"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="29">
+      <c r="A148" s="28">
         <v>60</v>
       </c>
-      <c r="B148" s="32">
+      <c r="B148" s="31">
         <v>44505</v>
       </c>
-      <c r="C148" s="37">
+      <c r="C148" s="36">
         <v>4</v>
       </c>
-      <c r="D148" s="84" t="s">
+      <c r="D148" s="83" t="s">
         <v>267</v>
       </c>
       <c r="E148" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F148" s="100" t="s">
+      <c r="F148" s="99" t="s">
         <v>270</v>
       </c>
-      <c r="G148" s="40" t="s">
+      <c r="G148" s="39" t="s">
         <v>269</v>
       </c>
       <c r="H148" s="10" t="s">
@@ -4811,23 +4776,23 @@
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="31"/>
-      <c r="B149" s="34">
+      <c r="A149" s="30"/>
+      <c r="B149" s="33">
         <v>44505</v>
       </c>
-      <c r="C149" s="36">
+      <c r="C149" s="35">
         <v>1</v>
       </c>
-      <c r="D149" s="85" t="s">
+      <c r="D149" s="84" t="s">
         <v>271</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F149" s="99" t="s">
+      <c r="F149" s="98" t="s">
         <v>272</v>
       </c>
-      <c r="G149" s="38" t="s">
+      <c r="G149" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H149" s="12" t="s">
@@ -4835,35 +4800,35 @@
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="30"/>
-      <c r="B150" s="33"/>
-      <c r="C150" s="35"/>
-      <c r="D150" s="76"/>
+      <c r="A150" s="29"/>
+      <c r="B150" s="32"/>
+      <c r="C150" s="34"/>
+      <c r="D150" s="75"/>
       <c r="E150" s="5"/>
-      <c r="F150" s="95"/>
-      <c r="G150" s="39"/>
+      <c r="F150" s="94"/>
+      <c r="G150" s="38"/>
       <c r="H150" s="11"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="31">
+      <c r="A151" s="30">
         <v>61</v>
       </c>
-      <c r="B151" s="46">
+      <c r="B151" s="45">
         <v>44506</v>
       </c>
-      <c r="C151" s="36">
+      <c r="C151" s="35">
         <v>2</v>
       </c>
-      <c r="D151" s="84" t="s">
+      <c r="D151" s="83" t="s">
         <v>273</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F151" s="100" t="s">
+      <c r="F151" s="99" t="s">
         <v>275</v>
       </c>
-      <c r="G151" s="59" t="s">
+      <c r="G151" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H151" s="12" t="s">
@@ -4871,35 +4836,35 @@
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="30"/>
-      <c r="B152" s="47"/>
-      <c r="C152" s="35"/>
-      <c r="D152" s="83"/>
+      <c r="A152" s="29"/>
+      <c r="B152" s="46"/>
+      <c r="C152" s="34"/>
+      <c r="D152" s="82"/>
       <c r="E152" s="5"/>
-      <c r="F152" s="95"/>
-      <c r="G152" s="39"/>
+      <c r="F152" s="94"/>
+      <c r="G152" s="38"/>
       <c r="H152" s="11"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="29">
+      <c r="A153" s="28">
         <v>62</v>
       </c>
-      <c r="B153" s="45">
+      <c r="B153" s="44">
         <v>44507</v>
       </c>
-      <c r="C153" s="37">
+      <c r="C153" s="36">
         <v>3</v>
       </c>
-      <c r="D153" s="80" t="s">
+      <c r="D153" s="79" t="s">
         <v>276</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F153" s="100" t="s">
+      <c r="F153" s="99" t="s">
         <v>278</v>
       </c>
-      <c r="G153" s="59" t="s">
+      <c r="G153" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H153" s="10" t="s">
@@ -4907,35 +4872,35 @@
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="31"/>
-      <c r="B154" s="46"/>
-      <c r="C154" s="36"/>
-      <c r="D154" s="69"/>
+      <c r="A154" s="30"/>
+      <c r="B154" s="45"/>
+      <c r="C154" s="35"/>
+      <c r="D154" s="68"/>
       <c r="E154" s="2"/>
-      <c r="F154" s="99"/>
-      <c r="G154" s="38"/>
+      <c r="F154" s="98"/>
+      <c r="G154" s="37"/>
       <c r="H154" s="12"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="29">
+      <c r="A155" s="28">
         <v>63</v>
       </c>
-      <c r="B155" s="32">
+      <c r="B155" s="31">
         <v>44508</v>
       </c>
-      <c r="C155" s="37">
+      <c r="C155" s="36">
         <v>4</v>
       </c>
-      <c r="D155" s="79" t="s">
+      <c r="D155" s="78" t="s">
         <v>279</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F155" s="100" t="s">
+      <c r="F155" s="99" t="s">
         <v>281</v>
       </c>
-      <c r="G155" s="40" t="s">
+      <c r="G155" s="39" t="s">
         <v>282</v>
       </c>
       <c r="H155" s="10" t="s">
@@ -4943,23 +4908,23 @@
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="31"/>
-      <c r="B156" s="34">
+      <c r="A156" s="30"/>
+      <c r="B156" s="33">
         <v>44508</v>
       </c>
-      <c r="C156" s="36">
+      <c r="C156" s="35">
         <v>1</v>
       </c>
-      <c r="D156" s="82" t="s">
+      <c r="D156" s="81" t="s">
         <v>283</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F156" s="99" t="s">
+      <c r="F156" s="98" t="s">
         <v>284</v>
       </c>
-      <c r="G156" s="38" t="s">
+      <c r="G156" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H156" s="12" t="s">
@@ -4967,35 +4932,35 @@
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="30"/>
-      <c r="B157" s="33"/>
-      <c r="C157" s="35"/>
-      <c r="D157" s="76"/>
+      <c r="A157" s="29"/>
+      <c r="B157" s="32"/>
+      <c r="C157" s="34"/>
+      <c r="D157" s="75"/>
       <c r="E157" s="5"/>
-      <c r="F157" s="95"/>
-      <c r="G157" s="39"/>
+      <c r="F157" s="94"/>
+      <c r="G157" s="38"/>
       <c r="H157" s="11"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="31">
+      <c r="A158" s="30">
         <v>64</v>
       </c>
-      <c r="B158" s="46">
+      <c r="B158" s="45">
         <v>44509</v>
       </c>
-      <c r="C158" s="36">
+      <c r="C158" s="35">
         <v>2</v>
       </c>
-      <c r="D158" s="82" t="s">
+      <c r="D158" s="81" t="s">
         <v>285</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F158" s="100" t="s">
+      <c r="F158" s="99" t="s">
         <v>287</v>
       </c>
-      <c r="G158" s="59" t="s">
+      <c r="G158" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H158" s="12" t="s">
@@ -5003,35 +4968,35 @@
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="30"/>
-      <c r="B159" s="47"/>
-      <c r="C159" s="35"/>
-      <c r="D159" s="83"/>
+      <c r="A159" s="29"/>
+      <c r="B159" s="46"/>
+      <c r="C159" s="34"/>
+      <c r="D159" s="82"/>
       <c r="E159" s="5"/>
-      <c r="F159" s="95"/>
-      <c r="G159" s="39"/>
+      <c r="F159" s="94"/>
+      <c r="G159" s="38"/>
       <c r="H159" s="11"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="29">
+      <c r="A160" s="28">
         <v>65</v>
       </c>
-      <c r="B160" s="45">
+      <c r="B160" s="44">
         <v>44510</v>
       </c>
-      <c r="C160" s="37">
+      <c r="C160" s="36">
         <v>3</v>
       </c>
-      <c r="D160" s="79" t="s">
+      <c r="D160" s="78" t="s">
         <v>288</v>
       </c>
       <c r="E160" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F160" s="100" t="s">
+      <c r="F160" s="99" t="s">
         <v>289</v>
       </c>
-      <c r="G160" s="59" t="s">
+      <c r="G160" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H160" s="10" t="s">
@@ -5039,35 +5004,35 @@
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="31"/>
-      <c r="B161" s="46"/>
-      <c r="C161" s="36"/>
-      <c r="D161" s="69"/>
+      <c r="A161" s="30"/>
+      <c r="B161" s="45"/>
+      <c r="C161" s="35"/>
+      <c r="D161" s="68"/>
       <c r="E161" s="2"/>
-      <c r="F161" s="99"/>
-      <c r="G161" s="38"/>
+      <c r="F161" s="98"/>
+      <c r="G161" s="37"/>
       <c r="H161" s="12"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="29">
+      <c r="A162" s="28">
         <v>66</v>
       </c>
-      <c r="B162" s="32">
+      <c r="B162" s="31">
         <v>44511</v>
       </c>
-      <c r="C162" s="37">
+      <c r="C162" s="36">
         <v>4</v>
       </c>
-      <c r="D162" s="79" t="s">
+      <c r="D162" s="78" t="s">
         <v>291</v>
       </c>
       <c r="E162" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F162" s="100" t="s">
+      <c r="F162" s="99" t="s">
         <v>292</v>
       </c>
-      <c r="G162" s="40" t="s">
+      <c r="G162" s="39" t="s">
         <v>293</v>
       </c>
       <c r="H162" s="10" t="s">
@@ -5075,23 +5040,23 @@
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="31"/>
-      <c r="B163" s="34">
+      <c r="A163" s="30"/>
+      <c r="B163" s="33">
         <v>44511</v>
       </c>
-      <c r="C163" s="36">
+      <c r="C163" s="35">
         <v>1</v>
       </c>
-      <c r="D163" s="82" t="s">
+      <c r="D163" s="81" t="s">
         <v>295</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F163" s="99" t="s">
+      <c r="F163" s="98" t="s">
         <v>296</v>
       </c>
-      <c r="G163" s="38" t="s">
+      <c r="G163" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H163" s="12" t="s">
@@ -5099,35 +5064,35 @@
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" s="30"/>
-      <c r="B164" s="33"/>
-      <c r="C164" s="35"/>
-      <c r="D164" s="76"/>
+      <c r="A164" s="29"/>
+      <c r="B164" s="32"/>
+      <c r="C164" s="34"/>
+      <c r="D164" s="75"/>
       <c r="E164" s="5"/>
-      <c r="F164" s="95"/>
-      <c r="G164" s="39"/>
+      <c r="F164" s="94"/>
+      <c r="G164" s="38"/>
       <c r="H164" s="11"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="31">
+      <c r="A165" s="30">
         <v>67</v>
       </c>
-      <c r="B165" s="46">
+      <c r="B165" s="45">
         <v>44512</v>
       </c>
-      <c r="C165" s="36">
+      <c r="C165" s="35">
         <v>2</v>
       </c>
-      <c r="D165" s="79" t="s">
+      <c r="D165" s="78" t="s">
         <v>297</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F165" s="100" t="s">
+      <c r="F165" s="99" t="s">
         <v>299</v>
       </c>
-      <c r="G165" s="59" t="s">
+      <c r="G165" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H165" s="12" t="s">
@@ -5135,35 +5100,35 @@
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="30"/>
-      <c r="B166" s="47"/>
-      <c r="C166" s="35"/>
-      <c r="D166" s="83"/>
+      <c r="A166" s="29"/>
+      <c r="B166" s="46"/>
+      <c r="C166" s="34"/>
+      <c r="D166" s="82"/>
       <c r="E166" s="5"/>
-      <c r="F166" s="95"/>
-      <c r="G166" s="39"/>
+      <c r="F166" s="94"/>
+      <c r="G166" s="38"/>
       <c r="H166" s="11"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="29">
+      <c r="A167" s="28">
         <v>68</v>
       </c>
-      <c r="B167" s="45">
+      <c r="B167" s="44">
         <v>44513</v>
       </c>
-      <c r="C167" s="37">
+      <c r="C167" s="36">
         <v>3</v>
       </c>
-      <c r="D167" s="79" t="s">
+      <c r="D167" s="78" t="s">
         <v>300</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F167" s="100" t="s">
+      <c r="F167" s="99" t="s">
         <v>302</v>
       </c>
-      <c r="G167" s="59" t="s">
+      <c r="G167" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H167" s="10" t="s">
@@ -5171,35 +5136,35 @@
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="30"/>
-      <c r="B168" s="47"/>
-      <c r="C168" s="35"/>
-      <c r="D168" s="83"/>
+      <c r="A168" s="29"/>
+      <c r="B168" s="46"/>
+      <c r="C168" s="34"/>
+      <c r="D168" s="82"/>
       <c r="E168" s="5"/>
-      <c r="F168" s="95"/>
-      <c r="G168" s="39"/>
+      <c r="F168" s="94"/>
+      <c r="G168" s="38"/>
       <c r="H168" s="11"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" s="29">
+      <c r="A169" s="28">
         <v>69</v>
       </c>
-      <c r="B169" s="45">
+      <c r="B169" s="44">
         <v>44514</v>
       </c>
-      <c r="C169" s="37">
+      <c r="C169" s="36">
         <v>1</v>
       </c>
-      <c r="D169" s="68" t="s">
+      <c r="D169" s="67" t="s">
         <v>303</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F169" s="100" t="s">
+      <c r="F169" s="99" t="s">
         <v>305</v>
       </c>
-      <c r="G169" s="59" t="s">
+      <c r="G169" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H169" s="10" t="s">
@@ -5207,35 +5172,35 @@
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="30"/>
-      <c r="B170" s="47"/>
-      <c r="C170" s="35"/>
-      <c r="D170" s="83"/>
+      <c r="A170" s="29"/>
+      <c r="B170" s="46"/>
+      <c r="C170" s="34"/>
+      <c r="D170" s="82"/>
       <c r="E170" s="5"/>
-      <c r="F170" s="95"/>
-      <c r="G170" s="39"/>
+      <c r="F170" s="94"/>
+      <c r="G170" s="38"/>
       <c r="H170" s="11"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="29">
+      <c r="A171" s="28">
         <v>70</v>
       </c>
-      <c r="B171" s="45">
+      <c r="B171" s="44">
         <v>44515</v>
       </c>
-      <c r="C171" s="37">
+      <c r="C171" s="36">
         <v>2</v>
       </c>
-      <c r="D171" s="68" t="s">
+      <c r="D171" s="67" t="s">
         <v>306</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F171" s="100" t="s">
+      <c r="F171" s="99" t="s">
         <v>308</v>
       </c>
-      <c r="G171" s="59" t="s">
+      <c r="G171" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H171" s="10" t="s">
@@ -5243,35 +5208,35 @@
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="31"/>
-      <c r="B172" s="46"/>
-      <c r="C172" s="36"/>
-      <c r="D172" s="69"/>
+      <c r="A172" s="30"/>
+      <c r="B172" s="45"/>
+      <c r="C172" s="35"/>
+      <c r="D172" s="68"/>
       <c r="E172" s="2"/>
-      <c r="F172" s="99"/>
-      <c r="G172" s="38"/>
+      <c r="F172" s="98"/>
+      <c r="G172" s="37"/>
       <c r="H172" s="12"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" s="60">
+      <c r="A173" s="59">
         <v>71</v>
       </c>
-      <c r="B173" s="45">
+      <c r="B173" s="44">
         <v>44516</v>
       </c>
-      <c r="C173" s="29">
+      <c r="C173" s="28">
         <v>3</v>
       </c>
-      <c r="D173" s="68" t="s">
+      <c r="D173" s="67" t="s">
         <v>309</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F173" s="100" t="s">
+      <c r="F173" s="99" t="s">
         <v>311</v>
       </c>
-      <c r="G173" s="51" t="s">
+      <c r="G173" s="50" t="s">
         <v>312</v>
       </c>
       <c r="H173" s="10" t="s">
@@ -5279,23 +5244,23 @@
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="61"/>
-      <c r="B174" s="46">
+      <c r="A174" s="60"/>
+      <c r="B174" s="45">
         <v>44516</v>
       </c>
-      <c r="C174" s="31">
+      <c r="C174" s="30">
         <v>1</v>
       </c>
-      <c r="D174" s="69" t="s">
+      <c r="D174" s="68" t="s">
         <v>313</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F174" s="99" t="s">
+      <c r="F174" s="98" t="s">
         <v>314</v>
       </c>
-      <c r="G174" s="38" t="s">
+      <c r="G174" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H174" s="12" t="s">
@@ -5303,35 +5268,35 @@
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="57"/>
-      <c r="B175" s="47"/>
-      <c r="C175" s="30"/>
-      <c r="D175" s="83"/>
+      <c r="A175" s="56"/>
+      <c r="B175" s="46"/>
+      <c r="C175" s="29"/>
+      <c r="D175" s="82"/>
       <c r="E175" s="5"/>
-      <c r="F175" s="95"/>
-      <c r="G175" s="52"/>
+      <c r="F175" s="94"/>
+      <c r="G175" s="51"/>
       <c r="H175" s="11"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="31">
+      <c r="A176" s="30">
         <v>72</v>
       </c>
-      <c r="B176" s="46">
+      <c r="B176" s="45">
         <v>44517</v>
       </c>
-      <c r="C176" s="36">
+      <c r="C176" s="35">
         <v>2</v>
       </c>
-      <c r="D176" s="68" t="s">
+      <c r="D176" s="67" t="s">
         <v>315</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F176" s="100" t="s">
+      <c r="F176" s="99" t="s">
         <v>317</v>
       </c>
-      <c r="G176" s="59" t="s">
+      <c r="G176" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H176" s="12" t="s">
@@ -5339,35 +5304,35 @@
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="31"/>
-      <c r="B177" s="46"/>
-      <c r="C177" s="36"/>
-      <c r="D177" s="69"/>
+      <c r="A177" s="30"/>
+      <c r="B177" s="45"/>
+      <c r="C177" s="35"/>
+      <c r="D177" s="68"/>
       <c r="E177" s="2"/>
-      <c r="F177" s="99"/>
-      <c r="G177" s="38"/>
+      <c r="F177" s="98"/>
+      <c r="G177" s="37"/>
       <c r="H177" s="12"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" s="29">
+      <c r="A178" s="28">
         <v>73</v>
       </c>
-      <c r="B178" s="32">
+      <c r="B178" s="31">
         <v>44518</v>
       </c>
-      <c r="C178" s="37">
+      <c r="C178" s="36">
         <v>3</v>
       </c>
-      <c r="D178" s="75" t="s">
+      <c r="D178" s="74" t="s">
         <v>318</v>
       </c>
       <c r="E178" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F178" s="100" t="s">
+      <c r="F178" s="99" t="s">
         <v>320</v>
       </c>
-      <c r="G178" s="40" t="s">
+      <c r="G178" s="39" t="s">
         <v>321</v>
       </c>
       <c r="H178" s="10" t="s">
@@ -5375,23 +5340,23 @@
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" s="31"/>
-      <c r="B179" s="34">
+      <c r="A179" s="30"/>
+      <c r="B179" s="33">
         <v>44518</v>
       </c>
-      <c r="C179" s="36">
+      <c r="C179" s="35">
         <v>1</v>
       </c>
-      <c r="D179" s="64" t="s">
+      <c r="D179" s="63" t="s">
         <v>322</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F179" s="99" t="s">
+      <c r="F179" s="98" t="s">
         <v>323</v>
       </c>
-      <c r="G179" s="38" t="s">
+      <c r="G179" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H179" s="12" t="s">
@@ -5399,35 +5364,35 @@
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="30"/>
-      <c r="B180" s="33"/>
-      <c r="C180" s="35"/>
-      <c r="D180" s="76"/>
+      <c r="A180" s="29"/>
+      <c r="B180" s="32"/>
+      <c r="C180" s="34"/>
+      <c r="D180" s="75"/>
       <c r="E180" s="5"/>
-      <c r="F180" s="95"/>
-      <c r="G180" s="39"/>
+      <c r="F180" s="94"/>
+      <c r="G180" s="38"/>
       <c r="H180" s="11"/>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A181" s="31">
+      <c r="A181" s="30">
         <v>74</v>
       </c>
-      <c r="B181" s="46">
+      <c r="B181" s="45">
         <v>44519</v>
       </c>
-      <c r="C181" s="36">
+      <c r="C181" s="35">
         <v>2</v>
       </c>
-      <c r="D181" s="75" t="s">
+      <c r="D181" s="74" t="s">
         <v>324</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F181" s="100" t="s">
+      <c r="F181" s="99" t="s">
         <v>326</v>
       </c>
-      <c r="G181" s="59" t="s">
+      <c r="G181" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H181" s="12" t="s">
@@ -5435,71 +5400,71 @@
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A182" s="30"/>
-      <c r="B182" s="47"/>
-      <c r="C182" s="35"/>
-      <c r="D182" s="83"/>
+      <c r="A182" s="29"/>
+      <c r="B182" s="46"/>
+      <c r="C182" s="34"/>
+      <c r="D182" s="82"/>
       <c r="E182" s="5"/>
-      <c r="F182" s="95"/>
-      <c r="G182" s="39"/>
+      <c r="F182" s="94"/>
+      <c r="G182" s="38"/>
       <c r="H182" s="11"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="29">
+      <c r="A183" s="28">
         <v>75</v>
       </c>
-      <c r="B183" s="45">
+      <c r="B183" s="44">
         <v>44520</v>
       </c>
-      <c r="C183" s="37">
+      <c r="C183" s="36">
         <v>1</v>
       </c>
-      <c r="D183" s="68" t="s">
+      <c r="D183" s="67" t="s">
         <v>327</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F183" s="100" t="s">
+      <c r="F183" s="99" t="s">
         <v>329</v>
       </c>
-      <c r="G183" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="H183" s="10" t="s">
+      <c r="G183" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H183" s="102" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="30"/>
-      <c r="B184" s="47"/>
-      <c r="C184" s="35"/>
-      <c r="D184" s="83"/>
+      <c r="A184" s="29"/>
+      <c r="B184" s="46"/>
+      <c r="C184" s="34"/>
+      <c r="D184" s="82"/>
       <c r="E184" s="5"/>
-      <c r="F184" s="95"/>
-      <c r="G184" s="39"/>
+      <c r="F184" s="94"/>
+      <c r="G184" s="38"/>
       <c r="H184" s="11"/>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="29">
+      <c r="A185" s="28">
         <v>76</v>
       </c>
-      <c r="B185" s="45">
+      <c r="B185" s="44">
         <v>44521</v>
       </c>
-      <c r="C185" s="37">
+      <c r="C185" s="36">
         <v>2</v>
       </c>
-      <c r="D185" s="68" t="s">
+      <c r="D185" s="67" t="s">
         <v>330</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F185" s="100" t="s">
+      <c r="F185" s="99" t="s">
         <v>332</v>
       </c>
-      <c r="G185" s="59" t="s">
+      <c r="G185" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H185" s="10" t="s">
@@ -5507,35 +5472,35 @@
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="30"/>
-      <c r="B186" s="47"/>
-      <c r="C186" s="35"/>
-      <c r="D186" s="83"/>
+      <c r="A186" s="29"/>
+      <c r="B186" s="46"/>
+      <c r="C186" s="34"/>
+      <c r="D186" s="82"/>
       <c r="E186" s="5"/>
-      <c r="F186" s="95"/>
-      <c r="G186" s="39"/>
+      <c r="F186" s="94"/>
+      <c r="G186" s="38"/>
       <c r="H186" s="11"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="29">
+      <c r="A187" s="28">
         <v>77</v>
       </c>
-      <c r="B187" s="45">
+      <c r="B187" s="44">
         <v>44522</v>
       </c>
-      <c r="C187" s="37">
+      <c r="C187" s="36">
         <v>1</v>
       </c>
-      <c r="D187" s="68" t="s">
+      <c r="D187" s="67" t="s">
         <v>333</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F187" s="100" t="s">
+      <c r="F187" s="99" t="s">
         <v>335</v>
       </c>
-      <c r="G187" s="59" t="s">
+      <c r="G187" s="58" t="s">
         <v>13</v>
       </c>
       <c r="H187" s="10" t="s">
@@ -5543,95 +5508,95 @@
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="30"/>
-      <c r="B188" s="47"/>
-      <c r="C188" s="35"/>
-      <c r="D188" s="83"/>
+      <c r="A188" s="29"/>
+      <c r="B188" s="46"/>
+      <c r="C188" s="34"/>
+      <c r="D188" s="82"/>
       <c r="E188" s="5"/>
-      <c r="F188" s="95"/>
-      <c r="G188" s="39"/>
+      <c r="F188" s="94"/>
+      <c r="G188" s="38"/>
       <c r="H188" s="12"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="29">
+      <c r="A189" s="28">
         <v>78</v>
       </c>
-      <c r="B189" s="45">
+      <c r="B189" s="44">
         <v>44523</v>
       </c>
-      <c r="C189" s="37">
+      <c r="C189" s="36">
         <v>2</v>
       </c>
-      <c r="D189" s="68" t="s">
+      <c r="D189" s="67" t="s">
         <v>336</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F189" s="100" t="s">
+      <c r="F189" s="99" t="s">
         <v>338</v>
       </c>
-      <c r="G189" s="49" t="s">
+      <c r="G189" s="48" t="s">
         <v>339</v>
       </c>
-      <c r="H189" s="53" t="s">
+      <c r="H189" s="52" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="31"/>
-      <c r="B190" s="46">
+      <c r="A190" s="30"/>
+      <c r="B190" s="45">
         <v>44523</v>
       </c>
-      <c r="C190" s="36">
+      <c r="C190" s="35">
         <v>1</v>
       </c>
-      <c r="D190" s="69" t="s">
+      <c r="D190" s="68" t="s">
         <v>340</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F190" s="99" t="s">
+      <c r="F190" s="98" t="s">
         <v>341</v>
       </c>
-      <c r="G190" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="H190" s="54" t="s">
+      <c r="G190" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H190" s="53" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="30"/>
-      <c r="B191" s="47"/>
-      <c r="C191" s="35"/>
-      <c r="D191" s="69"/>
+      <c r="A191" s="29"/>
+      <c r="B191" s="46"/>
+      <c r="C191" s="34"/>
+      <c r="D191" s="68"/>
       <c r="E191" s="2"/>
-      <c r="F191" s="99"/>
+      <c r="F191" s="98"/>
       <c r="G191" s="6"/>
-      <c r="H191" s="55"/>
+      <c r="H191" s="54"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="29">
+      <c r="A192" s="28">
         <v>79</v>
       </c>
-      <c r="B192" s="45">
+      <c r="B192" s="44">
         <v>44524</v>
       </c>
-      <c r="C192" s="58">
+      <c r="C192" s="57">
         <v>2</v>
       </c>
-      <c r="D192" s="68" t="s">
+      <c r="D192" s="67" t="s">
         <v>342</v>
       </c>
       <c r="E192" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F192" s="100" t="s">
+      <c r="F192" s="99" t="s">
         <v>344</v>
       </c>
-      <c r="G192" s="38" t="s">
+      <c r="G192" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H192" s="12" t="s">
@@ -5639,35 +5604,35 @@
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="30"/>
-      <c r="B193" s="47"/>
+      <c r="A193" s="29"/>
+      <c r="B193" s="46"/>
       <c r="C193" s="4"/>
-      <c r="D193" s="83"/>
+      <c r="D193" s="82"/>
       <c r="E193" s="5"/>
-      <c r="F193" s="95"/>
-      <c r="G193" s="39"/>
+      <c r="F193" s="94"/>
+      <c r="G193" s="38"/>
       <c r="H193" s="11"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="29">
+      <c r="A194" s="28">
         <v>80</v>
       </c>
-      <c r="B194" s="45">
+      <c r="B194" s="44">
         <v>44525</v>
       </c>
-      <c r="C194" s="37">
+      <c r="C194" s="36">
         <v>3</v>
       </c>
-      <c r="D194" s="68" t="s">
+      <c r="D194" s="67" t="s">
         <v>345</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F194" s="100" t="s">
+      <c r="F194" s="99" t="s">
         <v>347</v>
       </c>
-      <c r="G194" s="38" t="s">
+      <c r="G194" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H194" s="10" t="s">
@@ -5675,35 +5640,35 @@
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="30"/>
-      <c r="B195" s="47"/>
-      <c r="C195" s="35"/>
-      <c r="D195" s="83"/>
+      <c r="A195" s="29"/>
+      <c r="B195" s="46"/>
+      <c r="C195" s="34"/>
+      <c r="D195" s="82"/>
       <c r="E195" s="5"/>
-      <c r="F195" s="95"/>
-      <c r="G195" s="39"/>
+      <c r="F195" s="94"/>
+      <c r="G195" s="38"/>
       <c r="H195" s="11"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="29">
+      <c r="A196" s="28">
         <v>81</v>
       </c>
-      <c r="B196" s="45">
+      <c r="B196" s="44">
         <v>44526</v>
       </c>
-      <c r="C196" s="37">
+      <c r="C196" s="36">
         <v>1</v>
       </c>
-      <c r="D196" s="68" t="s">
+      <c r="D196" s="67" t="s">
         <v>348</v>
       </c>
       <c r="E196" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F196" s="100" t="s">
+      <c r="F196" s="99" t="s">
         <v>350</v>
       </c>
-      <c r="G196" s="38" t="s">
+      <c r="G196" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H196" s="10" t="s">
@@ -5711,35 +5676,35 @@
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="30"/>
-      <c r="B197" s="47"/>
-      <c r="C197" s="35"/>
-      <c r="D197" s="83"/>
+      <c r="A197" s="29"/>
+      <c r="B197" s="46"/>
+      <c r="C197" s="34"/>
+      <c r="D197" s="82"/>
       <c r="E197" s="5"/>
-      <c r="F197" s="95"/>
-      <c r="G197" s="39"/>
+      <c r="F197" s="94"/>
+      <c r="G197" s="38"/>
       <c r="H197" s="11"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A198" s="29">
+      <c r="A198" s="28">
         <v>82</v>
       </c>
-      <c r="B198" s="45">
+      <c r="B198" s="44">
         <v>44527</v>
       </c>
-      <c r="C198" s="37">
+      <c r="C198" s="36">
         <v>2</v>
       </c>
-      <c r="D198" s="68" t="s">
+      <c r="D198" s="67" t="s">
         <v>351</v>
       </c>
       <c r="E198" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F198" s="100" t="s">
+      <c r="F198" s="99" t="s">
         <v>353</v>
       </c>
-      <c r="G198" s="38" t="s">
+      <c r="G198" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H198" s="10" t="s">
@@ -5747,35 +5712,35 @@
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="30"/>
-      <c r="B199" s="47"/>
-      <c r="C199" s="35"/>
-      <c r="D199" s="83"/>
+      <c r="A199" s="29"/>
+      <c r="B199" s="46"/>
+      <c r="C199" s="34"/>
+      <c r="D199" s="82"/>
       <c r="E199" s="5"/>
-      <c r="F199" s="95"/>
-      <c r="G199" s="39"/>
+      <c r="F199" s="94"/>
+      <c r="G199" s="38"/>
       <c r="H199" s="11"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A200" s="29">
+      <c r="A200" s="28">
         <v>83</v>
       </c>
-      <c r="B200" s="45">
+      <c r="B200" s="44">
         <v>44528</v>
       </c>
-      <c r="C200" s="37">
+      <c r="C200" s="36">
         <v>3</v>
       </c>
-      <c r="D200" s="68" t="s">
+      <c r="D200" s="67" t="s">
         <v>354</v>
       </c>
       <c r="E200" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F200" s="100" t="s">
+      <c r="F200" s="99" t="s">
         <v>356</v>
       </c>
-      <c r="G200" s="38" t="s">
+      <c r="G200" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H200" s="10" t="s">
@@ -5783,35 +5748,35 @@
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A201" s="30"/>
-      <c r="B201" s="47"/>
-      <c r="C201" s="35"/>
-      <c r="D201" s="83"/>
+      <c r="A201" s="29"/>
+      <c r="B201" s="46"/>
+      <c r="C201" s="34"/>
+      <c r="D201" s="82"/>
       <c r="E201" s="5"/>
-      <c r="F201" s="95"/>
-      <c r="G201" s="39"/>
+      <c r="F201" s="94"/>
+      <c r="G201" s="38"/>
       <c r="H201" s="11"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="29">
+      <c r="A202" s="28">
         <v>84</v>
       </c>
-      <c r="B202" s="45">
+      <c r="B202" s="44">
         <v>44529</v>
       </c>
-      <c r="C202" s="37">
+      <c r="C202" s="36">
         <v>1</v>
       </c>
-      <c r="D202" s="68" t="s">
+      <c r="D202" s="67" t="s">
         <v>357</v>
       </c>
       <c r="E202" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F202" s="100" t="s">
+      <c r="F202" s="99" t="s">
         <v>359</v>
       </c>
-      <c r="G202" s="38" t="s">
+      <c r="G202" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H202" s="10" t="s">
@@ -5819,35 +5784,35 @@
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A203" s="30"/>
-      <c r="B203" s="47"/>
-      <c r="C203" s="35"/>
-      <c r="D203" s="83"/>
+      <c r="A203" s="29"/>
+      <c r="B203" s="46"/>
+      <c r="C203" s="34"/>
+      <c r="D203" s="82"/>
       <c r="E203" s="5"/>
-      <c r="F203" s="95"/>
-      <c r="G203" s="39"/>
+      <c r="F203" s="94"/>
+      <c r="G203" s="38"/>
       <c r="H203" s="11"/>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204" s="29">
+      <c r="A204" s="28">
         <v>85</v>
       </c>
-      <c r="B204" s="45">
+      <c r="B204" s="44">
         <v>44530</v>
       </c>
-      <c r="C204" s="37">
+      <c r="C204" s="36">
         <v>2</v>
       </c>
-      <c r="D204" s="68" t="s">
+      <c r="D204" s="67" t="s">
         <v>360</v>
       </c>
       <c r="E204" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F204" s="100" t="s">
+      <c r="F204" s="99" t="s">
         <v>362</v>
       </c>
-      <c r="G204" s="38" t="s">
+      <c r="G204" s="37" t="s">
         <v>13</v>
       </c>
       <c r="H204" s="10" t="s">
@@ -5855,22 +5820,22 @@
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A205" s="30"/>
-      <c r="B205" s="47"/>
-      <c r="C205" s="35"/>
-      <c r="D205" s="83"/>
+      <c r="A205" s="29"/>
+      <c r="B205" s="46"/>
+      <c r="C205" s="34"/>
+      <c r="D205" s="82"/>
       <c r="E205" s="5"/>
-      <c r="F205" s="95"/>
-      <c r="G205" s="39"/>
+      <c r="F205" s="94"/>
+      <c r="G205" s="38"/>
       <c r="H205" s="11"/>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B207" s="64"/>
-      <c r="C207" s="82" t="s">
+      <c r="B207" s="63"/>
+      <c r="C207" s="81" t="s">
         <v>363</v>
       </c>
       <c r="D207" s="2"/>
-      <c r="E207" s="102"/>
+      <c r="E207" s="101"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5878,6 +5843,6 @@
     <hyperlink ref="H31" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId3"/>
+  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId3"/>
 </worksheet>
 </file>